--- a/catalogo_mikado.xlsx
+++ b/catalogo_mikado.xlsx
@@ -129,7 +129,7 @@
     <t>Aceite limpiador hidrofílico con 14 aceites vegetales. Remueve todo el maquillaje.</t>
   </si>
   <si>
-    <t>Pokemon</t>
+    <t>Skin</t>
   </si>
 </sst>
 </file>

--- a/catalogo_mikado.xlsx
+++ b/catalogo_mikado.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANDRE\Documents\Antigravity Proyectos\Mikado\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39BE53FB-7BAC-4569-9432-41FE2412DDCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7035"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catálogo Mikado Skincare" sheetId="1" r:id="rId1"/>
@@ -129,13 +130,13 @@
     <t>Aceite limpiador hidrofílico con 14 aceites vegetales. Remueve todo el maquillaje.</t>
   </si>
   <si>
-    <t>Skin</t>
+    <t>Skinc</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;S/&quot;\ #,##0.00"/>
   </numFmts>
@@ -526,7 +527,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/catalogo_mikado.xlsx
+++ b/catalogo_mikado.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANDRE\Documents\Antigravity Proyectos\Mikado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39BE53FB-7BAC-4569-9432-41FE2412DDCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040"/>
   </bookViews>
   <sheets>
     <sheet name="Catálogo Mikado Skincare" sheetId="1" r:id="rId1"/>
@@ -124,19 +123,19 @@
     <t>Pure Cleansing Oil 200ml</t>
   </si>
   <si>
-    <t>Limpiadores</t>
-  </si>
-  <si>
     <t>Aceite limpiador hidrofílico con 14 aceites vegetales. Remueve todo el maquillaje.</t>
   </si>
   <si>
-    <t>Skinc</t>
+    <t>Tocobo</t>
+  </si>
+  <si>
+    <t>Limpiador</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;S/&quot;\ #,##0.00"/>
   </numFmts>
@@ -527,7 +526,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -701,13 +700,13 @@
         <v>32</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>33</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E7" s="6">
         <v>98</v>
@@ -719,7 +718,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/catalogo_mikado.xlsx
+++ b/catalogo_mikado.xlsx
@@ -5,21 +5,24 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANDRE\Documents\Antigravity Proyectos\Mikado\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANDRE\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20700" windowHeight="7200"/>
   </bookViews>
   <sheets>
     <sheet name="Catálogo Mikado Skincare" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo Mikado Skincare'!$A$1:$H$57</definedName>
+  </definedNames>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="234">
   <si>
     <t>Codigo</t>
   </si>
@@ -48,12 +51,6 @@
     <t>MKD-001</t>
   </si>
   <si>
-    <t>Beauty of Joseon</t>
-  </si>
-  <si>
-    <t>Relief Sun: Rice + Probiotics SPF50+ PA++++</t>
-  </si>
-  <si>
     <t>Solares</t>
   </si>
   <si>
@@ -66,9 +63,6 @@
     <t>COSRX</t>
   </si>
   <si>
-    <t>Advanced Snail 96 Mucin Power Essence 100ml</t>
-  </si>
-  <si>
     <t>Serums</t>
   </si>
   <si>
@@ -78,12 +72,6 @@
     <t>MKD-003</t>
   </si>
   <si>
-    <t>Anua</t>
-  </si>
-  <si>
-    <t>Heartleaf 77% Soothing Toner 250ml</t>
-  </si>
-  <si>
     <t>Tonicos</t>
   </si>
   <si>
@@ -93,24 +81,12 @@
     <t>MKD-004</t>
   </si>
   <si>
-    <t>Skin1004</t>
-  </si>
-  <si>
-    <t>Madagascar Centella Ampoule 100ml</t>
-  </si>
-  <si>
     <t>Serum concentrado 100% Centella Asiática. Calma e hidrata intensamente.</t>
   </si>
   <si>
     <t>MKD-005</t>
   </si>
   <si>
-    <t>Laneige</t>
-  </si>
-  <si>
-    <t>Lip Sleeping Mask EX [Berry] 20g</t>
-  </si>
-  <si>
     <t>Mascarillas</t>
   </si>
   <si>
@@ -120,26 +96,645 @@
     <t>MKD-006</t>
   </si>
   <si>
-    <t>Pure Cleansing Oil 200ml</t>
+    <t>Limpiadores</t>
   </si>
   <si>
     <t>Aceite limpiador hidrofílico con 14 aceites vegetales. Remueve todo el maquillaje.</t>
   </si>
   <si>
-    <t>Tocobo</t>
-  </si>
-  <si>
-    <t>Limpiador</t>
+    <t>APLB</t>
+  </si>
+  <si>
+    <t>Crema Corporal</t>
+  </si>
+  <si>
+    <t>Es una crema corporal hidratante y despigmentante, formulada con ácido tranexámico y niacinamida, diseñada para unificar el tono de la piel, aclarar manchas oscuras y calmar la sequedad sin dejar sensación pegajosa.</t>
+  </si>
+  <si>
+    <t>La Loción Corporal Glutathione Niacinamide de APLB aporta un efecto iluminador y suavizante a tu rutina diaria de cuidado corporal.</t>
+  </si>
+  <si>
+    <t>ARENCIA</t>
+  </si>
+  <si>
+    <t>CELIMAX</t>
+  </si>
+  <si>
+    <t>DR ALTHEA</t>
+  </si>
+  <si>
+    <t>MARY &amp; MAY</t>
+  </si>
+  <si>
+    <t>MEDICUBE</t>
+  </si>
+  <si>
+    <t>MIXSOON</t>
+  </si>
+  <si>
+    <t>NINELESS</t>
+  </si>
+  <si>
+    <t>PURITO</t>
+  </si>
+  <si>
+    <t>ROUND LAB</t>
+  </si>
+  <si>
+    <t>SEOUL 1988</t>
+  </si>
+  <si>
+    <t>SKIN 1004</t>
+  </si>
+  <si>
+    <t>TOCOBO</t>
+  </si>
+  <si>
+    <t>UNLEASHIA</t>
+  </si>
+  <si>
+    <t>Make up</t>
+  </si>
+  <si>
+    <t>Eye Cream</t>
+  </si>
+  <si>
+    <t>Booster</t>
+  </si>
+  <si>
+    <t>Hidratante</t>
+  </si>
+  <si>
+    <t>Kit</t>
+  </si>
+  <si>
+    <t>Set de Prueba The Real Noni Starter Kit</t>
+  </si>
+  <si>
+    <t>Kit de Prueba 9-Pasos</t>
+  </si>
+  <si>
+    <t>Set imprescindible con los esenciales de la línea Madagascar Centella en tamaño miniatura. Incluye limpiador, tónico, ampolla y cremas para mantener una rutina calmante e hidratante vayas a donde vayas.</t>
+  </si>
+  <si>
+    <t>Sérum facial concentrado formulado con extracto de hisopo sagrado. Calma las pieles irritadas, restaura la barrera cutánea y proporciona un impulso intensivo de hidratación y vitalidad. Perfecto para devolverle el confort, equilibrio y frescura a rostros cansados o sensibles.</t>
+  </si>
+  <si>
+    <t>Tratamiento intensivo para la mirada enriquecido con retinal y extracto de ginseng. Su fórmula suave pero eficaz ayuda a atenuar líneas de expresión, combatir ojeras y firmeza en la delicada zona de los ojos, dejando la mirada descansada, juvenil y rejuvenecida.</t>
+  </si>
+  <si>
+    <t>Un potente sérum regenerador que une el poder antioxidante del ginseng con la nutrición de la mucina de caracol. Repara la piel dañada, combate los signos del envejecimiento y mejora la elasticidad para revelar un rostro firme, hidratado y lleno de vitalidad natural.</t>
+  </si>
+  <si>
+    <t>Protector solar ligero diseñado especialmente para pieles mixtas a grasas. Ofrece alta protección UV mientras controla el exceso de sebo y los brillos durante todo el día. De acabado fresco y mate, no deja rastro blanco ni obstruye los poros.</t>
+  </si>
+  <si>
+    <t>El kit de iniciación perfecto para descubrir las bondades del fruto de Noni. Contiene una rutina completa en formato viaje diseñada para calmar, nutrir y revitalizar la piel estresada o sensible. Ideal para llevar a todos lados o probar antes del tamaño regular.</t>
+  </si>
+  <si>
+    <t>Limpiador facial en espuma microburbujeante enriquecido con extracto de Noni y activos antiacné. Limpia suavemente en profundidad, purifica los poros sin resecar y ayuda a calmar brotes y rojeces. Deja la piel limpia, suave y totalmente equilibrada.</t>
+  </si>
+  <si>
+    <t>Aceite limpiador con aceite de jojoba que disuelve eficazmente el maquillaje, la grasa acumulada y los puntos negros sin irritar. Se emulsiona fácilmente con agua, dejando la piel limpia, fresca, profundamente purificada y libre de impurezas.</t>
+  </si>
+  <si>
+    <t>Tratamiento especializado para difuminar manchas hiperpigmentadas y minimizar la apariencia de los poros dilatados. Formulado para unificar el tono de la piel, devolver el brillo natural y mejorar la textura cutánea, dejando el rostro uniforme y radiante.</t>
+  </si>
+  <si>
+    <t>Fotoprotección práctica y sin retoques complicados. Este protector solar en formato barra ofrece alta protección UV con efecto matificante. Controla la grasa, se desliza suavemente sobre la piel (incluso sobre el maquillaje) y es ideal para llevar en el bolso.</t>
+  </si>
+  <si>
+    <t>Booster antiedad avanzado enriquecido con retinal. Ayuda a estimular la renovación celular, afinar la textura de la piel y mejorar visiblemente la firmeza y elasticidad. Un potente aliado para atenuar arrugas y revitalizar la tez con resultados profesionales.</t>
+  </si>
+  <si>
+    <t>Ampolla nutritiva concentrada con extracto de superalimento Noni en presentación compacta. Aporta un alivio inmediato a la piel sensible, fortalece la barrera cutánea y proporciona una luminosidad saludable.</t>
+  </si>
+  <si>
+    <t>Crema hidratante y calmante de textura ligera tipo gel. Formulada para restaurar la piel dañada, suavizar rojeces e irritaciones y reparar la barrera cutánea. Aporta confort duradero y una hidratación profunda sin dejar sensación grasosa.</t>
+  </si>
+  <si>
+    <t>Tónico iluminador formulado con un 77.78% de extracto de arroz puro. Hidrata profundamente, suaviza las zonas ásperas y aporta un efecto glass skin radiante. Su textura bifásica equilibra la hidratación y nutrición de la piel cansada u opaca.</t>
+  </si>
+  <si>
+    <t>Mascarillas faciales impregnadas en colágeno marino de bajo peso molecular. Diseñadas para devolver la elasticidad, firmeza y humectación al rostro. Un tratamiento intensivo diario para lucir una piel tersa, lisa, rejuvenecida y llena de vida.</t>
+  </si>
+  <si>
+    <t>Mascarilla nutritiva enriquecida con ADN de salmón (PDRN). Ayuda a revitalizar la piel, potenciar la elasticidad y regenerar los tejidos apagados o dañados. Proporciona una recarga de hidratación y un acabado suave, terso y luminoso.</t>
+  </si>
+  <si>
+    <t>Mascarilla de gel refrescante que se adhiere perfectamente al contorno facial para una máxima absorción de activos. Calma al instante la piel estresada, cierra visiblemente los poros e hidrata en profundidad, dejando un efecto de spa en casa.</t>
+  </si>
+  <si>
+    <t>Crema hidratante iluminadora formulada con alta concentración de vitamina C. Ayuda a aclarar manchas, combatir la opacidad y proteger el rostro contra los radicales libres. Para una piel visiblemente más brillante, uniforme y vital.</t>
+  </si>
+  <si>
+    <t>Descubre la rutina coreana minimalista en su máxima expresión. Este kit contiene 9 muestras esenciales para limpiar, tonificar e hidratar la piel según sus necesidades. Perfecto para viajes o para probar los favoritos de la marca Mixsoon.</t>
+  </si>
+  <si>
+    <t>Aceite limpiador formulado con ingredientes naturales que retira eficazmente el maquillaje de larga duración, protector solar e impurezas de los poros. Mantiene la piel suave e hidratada tras el lavado sin romper la barrera cutánea.</t>
+  </si>
+  <si>
+    <t>Crema facial de fórmula limpia e ingredientes esenciales que proporciona hidratación profunda y duradera. Restaura la flexibilidad cutánea y calma la irritación sin obstruir poros. Ideal para todo tipo de pieles, incluso las más sensibles.</t>
+  </si>
+  <si>
+    <t>Esencia pura concentrada al 100% en extracto de Centella Asiática. Alivia de inmediato el enrojecimiento, disminuye inflamaciones y refuerza la barrera protectora de la piel. Indispensable para pieles sensibles, reactivas o con tendencia al acné.</t>
+  </si>
+  <si>
+    <t>Esencia viral rica en aminoácidos procedentes de la fermentación de soja. Funciona como exfoliante suave y tratamiento ultra-hidratante: remueve células muertas, regula el sebo y deja la textura de la piel sumamente suave y reluciente.</t>
+  </si>
+  <si>
+    <t>Sérum formulado con ácido azelaico, ideal para tratar el acné, atenuar marcas post-inflamatorias y controlar las rojeces. Unifica la textura y el tono del rostro mientras limpia suavemente los poros, manteniendo la piel clara y uniforme.</t>
+  </si>
+  <si>
+    <t>Sérum reconfortante enriquecido con extracto de Centella Asiática y niacinamida. Calma al instante la piel irritada, combate brotes y ayuda a reparar la barrera cutánea dañada. Su fórmula suave aporta hidratación equilibrada sin recargar la piel.</t>
+  </si>
+  <si>
+    <t>Crema hidratante intensiva a base de extracto de bambú y pantenol (Pro-Vitamina B5). Fortalece de inmediato la barrera cutánea, sella la humedad y protege la piel sensible del estrés ambiental. Deja el rostro reconfortado, elástico y saludable.</t>
+  </si>
+  <si>
+    <t>Protector solar en formato cushion práctico y portátil. Permite reaplicar la protección solar a lo largo del día sin alterar el maquillaje. Aporta un efecto refrescante, calmante e hidratante con acabado natural y sin residuo pegajoso.</t>
+  </si>
+  <si>
+    <t>Crema especializada para el contorno de ojos formulada con retinal y activos tradicionales. Ayuda a atenuar líneas de expresión, reafirmar los párpados y reducir la apariencia de cansancio. Deja la zona periocular firme, suave e hidratada.</t>
+  </si>
+  <si>
+    <t>Sérum antiedad potente diseñado para combatir los signos del paso del tiempo. Estimula la renovación celular, mejora la firmeza y alisa las arrugas finas, dejando el rostro visiblemente más joven, firme y uniforme.</t>
+  </si>
+  <si>
+    <t>Limpiador facial suave enriquecido con Centella Asiática de Madagascar. Elimina suciedad, restos de maquillaje y exceso de sebo de forma delicada, manteniendo el pH natural de la piel e impidiendo la tirantez o resequedad tras la limpieza.</t>
+  </si>
+  <si>
+    <t>Crema en gel ultra-ligera enriquecida con sal rosada del Himalaya. Ayuda a minimizar los poros dilatados, regula el exceso de grasa y proporciona una frescura e hidratación equilibrada ideal para pieles mixtas a grasas.</t>
+  </si>
+  <si>
+    <t>Protección solar de amplio espectro con efecto terciopelo. Su fórmula ayuda a controlar el sebo y la visibilidad de los poros mientras protege de los rayos UV. Deja un acabado suave, mate y sedoso sin sensación pesada.</t>
+  </si>
+  <si>
+    <t>Crema hidratante diseñada para reparar y calmar pieles sensibilizadas o irritadas. Enriquecida con ceramidas y centella asiática, restaura la barrera cutánea manteniendo el rostro hidratado, suave y libre de rojeces.</t>
+  </si>
+  <si>
+    <t>Set de mini ampollas altamente concentradas. Ideales para probar diferentes tratamientos según las necesidades diarias de tu piel: hidratación, calma, luminosidad o cuidado de poros en un formato práctico y portable.</t>
+  </si>
+  <si>
+    <t>Tónico exfoliante suave con AHA y sal rosada del Himalaya. Limpia a fondo los poros, elimina células muertas y prepara la piel para los siguientes pasos de la rutina, dejándola lisa, uniforme y libre de exceso de sebo.</t>
+  </si>
+  <si>
+    <t>Espuma de limpieza profunda enriquecida con extracto de sal rosada. Elimina eficazmente las impurezas acumuladas en los poros y limpia el exceso de grasa, manteniendo la piel fresca, clara y equilibrada.</t>
+  </si>
+  <si>
+    <t>Contorno de ojos formulado con Probio-Cica fermentada y Bakuchiol (la alternativa natural al retinol). Suaviza las líneas de expresión, fortalece la barrera de la piel delicada y combate la hinchazón y las ojeras sin irritar.</t>
+  </si>
+  <si>
+    <t>Tónico diario exfoliante e hidratante enriquecido con PHA. Remueve suavemente las células muertas sin irritar la piel, calma las rojeces y equilibra el rostro, dejándolo preparado para una absorción óptima de tus sérums.</t>
+  </si>
+  <si>
+    <t>Ampolla concentrada en formato mini con microcápsulas iluminadoras. Ayuda a unificar el tono de la piel, atenúa manchas e hiperpigmentación y devuelve la luminosidad natural a los rostros fatigados.</t>
+  </si>
+  <si>
+    <t>Bloqueador solar físico de textura ultraligera que se absorbe sin dejar capa blanca ni sensación grasa. Ofrece alta protección UV mientras calma la piel sensible gracias a su contenido de Centella Asiática.</t>
+  </si>
+  <si>
+    <t>Protector solar de base acuosa formulado con extracto de mungo y ácido hialurónico. Se absorbe al instante aportando una hidratación profunda y fresca. No deja sensación grasosa ni marcas blancas, perfecto para el uso diario.</t>
+  </si>
+  <si>
+    <t>Aceite labial nutritivo que combina un toque de color jugoso con un ligero efecto plumping (volumen). Enriquecido con extractos de bayas, aporta hidratación duradera, suavidad extrema y un acabado superbrillante no pegajoso.</t>
+  </si>
+  <si>
+    <t>Limpiador facial en espuma enriquecido con arcilla rosa y extracto de coco. Absorbe las impurezas y el exceso de grasa atrapados en los poros mientras mantiene la hidratación natural de la piel sin sensación de tirantez.</t>
+  </si>
+  <si>
+    <t>Tratamiento fotoprotector completo con 3 versiones de bloqueadores solares de la marca. La opción perfecta para probar o adaptar el tipo de protección solar a las necesidades diarias de tu piel (en barra, crema o textura acuosa).</t>
+  </si>
+  <si>
+    <t>Paleta de sombras con una combinación perfecta de tonos mate sedosos y destellos deslumbrantes. Altamente pigmentadas y fáciles de difuminar, ideales para crear looks diarios sutiles o maquillajes de noche impactantes.</t>
+  </si>
+  <si>
+    <t>Gel fijador de cejas de larga duración que peina, define y mantiene cada pelo en su lugar durante todo el día. No deja residuos blancos ni sensación rígida, logrando un acabado natural y pulido.</t>
+  </si>
+  <si>
+    <t>Tamaño</t>
+  </si>
+  <si>
+    <t>50ml</t>
+  </si>
+  <si>
+    <t>100ml</t>
+  </si>
+  <si>
+    <t>NO TENGO</t>
+  </si>
+  <si>
+    <t>200ml</t>
+  </si>
+  <si>
+    <t>300ml</t>
+  </si>
+  <si>
+    <t>50g</t>
+  </si>
+  <si>
+    <t>30ml</t>
+  </si>
+  <si>
+    <t>10ml</t>
+  </si>
+  <si>
+    <t>40ml</t>
+  </si>
+  <si>
+    <t>155ml</t>
+  </si>
+  <si>
+    <t>150ml</t>
+  </si>
+  <si>
+    <t>19g</t>
+  </si>
+  <si>
+    <t>15ml</t>
+  </si>
+  <si>
+    <t>210ml</t>
+  </si>
+  <si>
+    <t>125ml</t>
+  </si>
+  <si>
+    <t>75ml</t>
+  </si>
+  <si>
+    <t>20ml</t>
+  </si>
+  <si>
+    <t>4g</t>
+  </si>
+  <si>
+    <t>N°3</t>
+  </si>
+  <si>
+    <t>11g cada uno</t>
+  </si>
+  <si>
+    <t>20ml-30ml cada uno</t>
+  </si>
+  <si>
+    <t>60ml</t>
+  </si>
+  <si>
+    <t>28g</t>
+  </si>
+  <si>
+    <t>195ml</t>
+  </si>
+  <si>
+    <t>55g</t>
+  </si>
+  <si>
+    <t>400g</t>
+  </si>
+  <si>
+    <t>N°1</t>
+  </si>
+  <si>
+    <t>MKD-007</t>
+  </si>
+  <si>
+    <t>MKD-008</t>
+  </si>
+  <si>
+    <t>MKD-009</t>
+  </si>
+  <si>
+    <t>MKD-010</t>
+  </si>
+  <si>
+    <t>MKD-011</t>
+  </si>
+  <si>
+    <t>MKD-012</t>
+  </si>
+  <si>
+    <t>MKD-013</t>
+  </si>
+  <si>
+    <t>MKD-014</t>
+  </si>
+  <si>
+    <t>MKD-015</t>
+  </si>
+  <si>
+    <t>MKD-016</t>
+  </si>
+  <si>
+    <t>MKD-017</t>
+  </si>
+  <si>
+    <t>MKD-018</t>
+  </si>
+  <si>
+    <t>MKD-019</t>
+  </si>
+  <si>
+    <t>MKD-020</t>
+  </si>
+  <si>
+    <t>MKD-021</t>
+  </si>
+  <si>
+    <t>MKD-022</t>
+  </si>
+  <si>
+    <t>MKD-023</t>
+  </si>
+  <si>
+    <t>MKD-024</t>
+  </si>
+  <si>
+    <t>MKD-025</t>
+  </si>
+  <si>
+    <t>MKD-026</t>
+  </si>
+  <si>
+    <t>MKD-027</t>
+  </si>
+  <si>
+    <t>MKD-028</t>
+  </si>
+  <si>
+    <t>MKD-029</t>
+  </si>
+  <si>
+    <t>MKD-030</t>
+  </si>
+  <si>
+    <t>MKD-031</t>
+  </si>
+  <si>
+    <t>MKD-032</t>
+  </si>
+  <si>
+    <t>MKD-033</t>
+  </si>
+  <si>
+    <t>MKD-034</t>
+  </si>
+  <si>
+    <t>MKD-035</t>
+  </si>
+  <si>
+    <t>MKD-036</t>
+  </si>
+  <si>
+    <t>MKD-037</t>
+  </si>
+  <si>
+    <t>MKD-038</t>
+  </si>
+  <si>
+    <t>MKD-039</t>
+  </si>
+  <si>
+    <t>MKD-040</t>
+  </si>
+  <si>
+    <t>MKD-041</t>
+  </si>
+  <si>
+    <t>MKD-042</t>
+  </si>
+  <si>
+    <t>MKD-043</t>
+  </si>
+  <si>
+    <t>MKD-044</t>
+  </si>
+  <si>
+    <t>MKD-045</t>
+  </si>
+  <si>
+    <t>MKD-046</t>
+  </si>
+  <si>
+    <t>MKD-047</t>
+  </si>
+  <si>
+    <t>MKD-048</t>
+  </si>
+  <si>
+    <t>MKD-049</t>
+  </si>
+  <si>
+    <t>MKD-050</t>
+  </si>
+  <si>
+    <t>MKD-051</t>
+  </si>
+  <si>
+    <t>MKD-052</t>
+  </si>
+  <si>
+    <t>MKD-053</t>
+  </si>
+  <si>
+    <t>MKD-054</t>
+  </si>
+  <si>
+    <t>MKD-055</t>
+  </si>
+  <si>
+    <t>MKD-056</t>
+  </si>
+  <si>
+    <t>Bloqueador Cushion</t>
+  </si>
+  <si>
+    <t>Paleta de Sombras N°3</t>
+  </si>
+  <si>
+    <t>Gel de Cejas N°1</t>
+  </si>
+  <si>
+    <t>Set de 3 Bloqueadores - 11g</t>
+  </si>
+  <si>
+    <t>Relief Sun: Rice + Probiotics SPF50+ PA++++ - 50ml</t>
+  </si>
+  <si>
+    <t>Advanced Snail 96 Mucin Power Essence - 100ml</t>
+  </si>
+  <si>
+    <t>Heartleaf 77% Soothing Toner - 250ml</t>
+  </si>
+  <si>
+    <t>Madagascar Centella Ampoule - 100ml</t>
+  </si>
+  <si>
+    <t>Lip Sleeping Mask EX [Berry] - 20g</t>
+  </si>
+  <si>
+    <t>Pure Cleansing Oil - 200ml</t>
+  </si>
+  <si>
+    <t>Tranexamic Acid Niacinamide Body Lotion - 300ml</t>
+  </si>
+  <si>
+    <t>Loción Corporal Glutathione Niacinamide - 300ml</t>
+  </si>
+  <si>
+    <t>Holy Hyssop Serum 30 - 50g</t>
+  </si>
+  <si>
+    <t>Sérum Contorno de Ojos Revive Eye Serum - 30ml</t>
+  </si>
+  <si>
+    <t>Revive Serum: Ginseng + Snail Mucin - 10ml</t>
+  </si>
+  <si>
+    <t>Protector Solar Oil Control Light Sunscreen - 40ml</t>
+  </si>
+  <si>
+    <t>Limpiador en Burbujas para Acné The Real Noni - 155ml</t>
+  </si>
+  <si>
+    <t>Aceite Limpiador Derma Nature Fresh Blackhead Jojoba Cleansing Oil - 150ml</t>
+  </si>
+  <si>
+    <t>Sérum Iluminador Pore + Dark Spot Brightening - 30ml</t>
+  </si>
+  <si>
+    <t>Protector Solar en Barra Oil Control Mattifying - 19g</t>
+  </si>
+  <si>
+    <t>Sérum Facial The Vita-A Retinal Shot Tightening Booster - 15ml</t>
+  </si>
+  <si>
+    <t>Ampolla Facial Noni Ampoule Calming + Radiance - 100ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ampolla Facial Noni Ampoule Calming + Radiance - 30ml </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ampolla Facial Noni Ampoule Calming + Radiance - 50ml </t>
+  </si>
+  <si>
+    <t>Crema 345 Relief - 50ml</t>
+  </si>
+  <si>
+    <t>Tónico de Arroz - 150ml</t>
+  </si>
+  <si>
+    <t>Mask Collagen - 400g</t>
+  </si>
+  <si>
+    <t>Mascarilla de Salmón - 28g</t>
+  </si>
+  <si>
+    <t>Mascarilla Gel - 75ml</t>
+  </si>
+  <si>
+    <t>Crema Hidratante Vitamin C - 55g</t>
+  </si>
+  <si>
+    <t>Aceite Limpiador - 195ml</t>
+  </si>
+  <si>
+    <t>Esencia Centella Asiática - 100ml</t>
+  </si>
+  <si>
+    <t>Crema Hidratante - 50ml</t>
+  </si>
+  <si>
+    <t>Bean Essence - 50ml</t>
+  </si>
+  <si>
+    <t>Ácido Azelaico - 30ml</t>
+  </si>
+  <si>
+    <t>Serum Centella - 60ml</t>
+  </si>
+  <si>
+    <t>Crema con Pantenol Mighty Bamboo - 100ml</t>
+  </si>
+  <si>
+    <t>Retinal Crema Antiedad para Ojos - 30ml</t>
+  </si>
+  <si>
+    <t>Retinal Serum - 30ml</t>
+  </si>
+  <si>
+    <t>Espuma Limpiadora Madagascar Centella - 125ml</t>
+  </si>
+  <si>
+    <t>Crema Hidratante Madagascar Centella Poremizing Light Gel Cream - 75ml</t>
+  </si>
+  <si>
+    <t>Protector Solar Madagascar Centella Poremizing Velvet Finish Sunscreen - 50ml</t>
+  </si>
+  <si>
+    <t>Kit de viaje Madagascar Centella - 30ml</t>
+  </si>
+  <si>
+    <t>Crema Calmante Madagascar Centella Soothing Cream - 75ml</t>
+  </si>
+  <si>
+    <t>Mini Ampolla Facial - 30ml</t>
+  </si>
+  <si>
+    <t>Tónico Facial Madagascar Centella Poremizing Clear Toner - 210ml</t>
+  </si>
+  <si>
+    <t>Espuma Limpiadora Madagascar Centella Poremizing Deep Cleansing Foam - 125ml</t>
+  </si>
+  <si>
+    <t>Crema de Ojos Madagascar Centella Probio-Cica Bakuchiol - 20ml</t>
+  </si>
+  <si>
+    <t>Tónico Madagascar Centella Toning Toner - 210ml</t>
+  </si>
+  <si>
+    <t>Mini Ampolla Facial Iluminadora Madagascar Centella Tone Brightening Capsule Ampoule Mini - 30ml</t>
+  </si>
+  <si>
+    <t>Protector Solar Ligero Madagascar Centella Air Fit - 50ml</t>
+  </si>
+  <si>
+    <t>Protector Solar Bio Watery Sun Cream - 50ml</t>
+  </si>
+  <si>
+    <t>Aceite Labial Juicy Berry Plumping Lip Oil - 4g</t>
+  </si>
+  <si>
+    <t>Espuma Limpiadora Coconut Clay - 150ml</t>
+  </si>
+  <si>
+    <t>BEAUTY OF JOSEON</t>
+  </si>
+  <si>
+    <t>ANUA</t>
+  </si>
+  <si>
+    <t>LANEIGE</t>
+  </si>
+  <si>
+    <t>Precio Fijo</t>
+  </si>
+  <si>
+    <t>Stock Total</t>
+  </si>
+  <si>
+    <t>I'M FROM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;S/&quot;\ #,##0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,8 +754,16 @@
       <color rgb="FF2D2727"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -173,8 +776,20 @@
         <bgColor rgb="FFD48C95"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -184,16 +799,42 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFEFE8E1"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FFEFE8E1"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FFEFE8E1"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFEFE8E1"/>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -201,11 +842,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -225,6 +867,13 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -527,19 +1176,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:N57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="74.140625" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="50" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="8" max="8" width="64.7109375" customWidth="1"/>
+    <col min="9" max="9" width="5.42578125" style="13" customWidth="1"/>
+    <col min="10" max="10" width="20.42578125" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="11"/>
+    <col min="12" max="12" width="19.85546875" customWidth="1"/>
+    <col min="13" max="13" width="15.5703125" style="11" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -564,164 +1220,2034 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="J1" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="N1" s="2">
+        <f>SUM(F2:F937)</f>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="E2" s="7">
+        <v>93.333333333333329</v>
+      </c>
+      <c r="F2" s="8">
+        <v>2</v>
+      </c>
+      <c r="G2" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="H2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="J2" s="7">
+        <v>84</v>
+      </c>
+      <c r="K2" s="14">
+        <f>E2*(1-G2)</f>
+        <v>84</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="6">
+      <c r="B3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="7">
+        <v>110</v>
+      </c>
+      <c r="F3" s="8">
+        <v>2</v>
+      </c>
+      <c r="G3" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="7">
+        <v>88</v>
+      </c>
+      <c r="K3" s="14">
+        <f t="shared" ref="K3:K57" si="0">E3*(1-G3)</f>
+        <v>88</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="7">
+        <v>98.888888888888886</v>
+      </c>
+      <c r="F4" s="8">
+        <v>0</v>
+      </c>
+      <c r="G4" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="7">
+        <v>89</v>
+      </c>
+      <c r="K4" s="14">
+        <f t="shared" si="0"/>
+        <v>89</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="M4" s="12"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="7">
+        <v>102.22222222222221</v>
+      </c>
+      <c r="F5" s="8">
+        <v>0</v>
+      </c>
+      <c r="G5" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="7">
+        <v>92</v>
+      </c>
+      <c r="K5" s="14">
+        <f t="shared" si="0"/>
+        <v>92</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="7">
+        <v>75</v>
+      </c>
+      <c r="F6" s="8">
+        <v>0</v>
+      </c>
+      <c r="G6" s="9">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="7">
+        <v>75</v>
+      </c>
+      <c r="K6" s="14">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="7">
+        <v>99</v>
+      </c>
+      <c r="F7" s="8">
+        <v>2</v>
+      </c>
+      <c r="G7" s="9">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" s="7">
+        <v>99</v>
+      </c>
+      <c r="K7" s="14">
+        <f t="shared" si="0"/>
+        <v>99</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="7">
+        <v>117.64705882352942</v>
+      </c>
+      <c r="F8" s="8">
+        <v>1</v>
+      </c>
+      <c r="G8" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="7">
+        <v>100</v>
+      </c>
+      <c r="K8" s="14">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="7">
+        <v>111.11111111111111</v>
+      </c>
+      <c r="F9" s="8">
+        <v>1</v>
+      </c>
+      <c r="G9" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="7">
+        <v>100</v>
+      </c>
+      <c r="K9" s="14">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="7">
+        <v>123.75</v>
+      </c>
+      <c r="F10" s="8">
+        <v>3</v>
+      </c>
+      <c r="G10" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J10" s="7">
+        <v>99</v>
+      </c>
+      <c r="K10" s="14">
+        <f t="shared" si="0"/>
+        <v>99</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="7">
+        <v>88.421052631578945</v>
+      </c>
+      <c r="F11" s="8">
+        <v>2</v>
+      </c>
+      <c r="G11" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J11" s="7">
+        <v>84</v>
+      </c>
+      <c r="K11" s="14">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="7">
+        <v>22.222222222222221</v>
+      </c>
+      <c r="F12" s="8">
+        <v>2</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="J12" s="7">
+        <v>20</v>
+      </c>
+      <c r="K12" s="14">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="7">
+        <v>96.842105263157904</v>
+      </c>
+      <c r="F13" s="8">
+        <v>2</v>
+      </c>
+      <c r="G13" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="J13" s="7">
+        <v>92</v>
+      </c>
+      <c r="K13" s="14">
+        <f t="shared" si="0"/>
+        <v>92</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="7">
+        <v>110</v>
+      </c>
+      <c r="F14" s="8">
+        <v>6</v>
+      </c>
+      <c r="G14" s="9">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="J14" s="7">
+        <v>110</v>
+      </c>
+      <c r="K14" s="14">
+        <f t="shared" si="0"/>
+        <v>110</v>
+      </c>
+      <c r="L14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="7">
+        <v>110</v>
+      </c>
+      <c r="F15" s="8">
+        <v>1</v>
+      </c>
+      <c r="G15" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="J15" s="7">
+        <v>99</v>
+      </c>
+      <c r="K15" s="14">
+        <f t="shared" si="0"/>
+        <v>99</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="7">
+        <v>104.21052631578948</v>
+      </c>
+      <c r="F16" s="8">
+        <v>2</v>
+      </c>
+      <c r="G16" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J16" s="7">
+        <v>99</v>
+      </c>
+      <c r="K16" s="14">
+        <f t="shared" si="0"/>
+        <v>99</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="7">
+        <v>105.55555555555556</v>
+      </c>
+      <c r="F17" s="8">
+        <v>1</v>
+      </c>
+      <c r="G17" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J17" s="7">
+        <v>95</v>
+      </c>
+      <c r="K17" s="14">
+        <f t="shared" si="0"/>
+        <v>95</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="7">
+        <v>92</v>
+      </c>
+      <c r="F18" s="8">
+        <v>2</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J18" s="7">
+        <v>92</v>
+      </c>
+      <c r="K18" s="14">
+        <f t="shared" si="0"/>
+        <v>92</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="7">
+        <v>123.75</v>
+      </c>
+      <c r="F19" s="8">
+        <v>6</v>
+      </c>
+      <c r="G19" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="J19" s="7">
+        <v>99</v>
+      </c>
+      <c r="K19" s="14">
+        <f t="shared" si="0"/>
+        <v>99</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="7">
+        <v>141.1764705882353</v>
+      </c>
+      <c r="F20" s="8">
+        <v>3</v>
+      </c>
+      <c r="G20" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="J20" s="7">
+        <v>120</v>
+      </c>
+      <c r="K20" s="14">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="7">
+        <v>108.23529411764706</v>
+      </c>
+      <c r="F21" s="8">
+        <v>1</v>
+      </c>
+      <c r="G21" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="J21" s="7">
+        <v>92</v>
+      </c>
+      <c r="K21" s="14">
+        <f t="shared" si="0"/>
+        <v>92</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="7">
+        <v>131.25</v>
+      </c>
+      <c r="F22" s="8">
+        <v>1</v>
+      </c>
+      <c r="G22" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="J22" s="7">
+        <v>105</v>
+      </c>
+      <c r="K22" s="14">
+        <f t="shared" si="0"/>
+        <v>105</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" s="7">
+        <v>100</v>
+      </c>
+      <c r="F23" s="8">
+        <v>4</v>
+      </c>
+      <c r="G23" s="9">
+        <v>0</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="J23" s="7">
+        <v>100</v>
+      </c>
+      <c r="K23" s="14">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="7">
+        <v>121.11111111111111</v>
+      </c>
+      <c r="F24" s="8">
+        <v>1</v>
+      </c>
+      <c r="G24" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="J24" s="7">
+        <v>109</v>
+      </c>
+      <c r="K24" s="14">
+        <f t="shared" si="0"/>
+        <v>109</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="7">
+        <v>128</v>
+      </c>
+      <c r="F25" s="8">
+        <v>1</v>
+      </c>
+      <c r="G25" s="9">
+        <v>0</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="J25" s="7">
+        <v>128</v>
+      </c>
+      <c r="K25" s="14">
+        <f t="shared" si="0"/>
+        <v>128</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" s="7">
+        <v>25.882352941176471</v>
+      </c>
+      <c r="F26" s="8">
+        <v>2</v>
+      </c>
+      <c r="G26" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="J26" s="7">
+        <v>22</v>
+      </c>
+      <c r="K26" s="14">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="7">
+        <v>109</v>
+      </c>
+      <c r="F27" s="8">
+        <v>1</v>
+      </c>
+      <c r="G27" s="9">
+        <v>0</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="J27" s="7">
+        <v>109</v>
+      </c>
+      <c r="K27" s="14">
+        <f t="shared" si="0"/>
+        <v>109</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" s="7">
+        <v>109</v>
+      </c>
+      <c r="F28" s="8">
+        <v>2</v>
+      </c>
+      <c r="G28" s="9">
+        <v>0</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J28" s="7">
+        <v>109</v>
+      </c>
+      <c r="K28" s="14">
+        <f t="shared" si="0"/>
+        <v>109</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E29" s="7">
+        <v>25</v>
+      </c>
+      <c r="F29" s="8">
+        <v>10</v>
+      </c>
+      <c r="G29" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="J29" s="7">
+        <v>20</v>
+      </c>
+      <c r="K29" s="14">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="L29" s="6"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="7">
+        <v>102</v>
+      </c>
+      <c r="F30" s="8">
+        <v>1</v>
+      </c>
+      <c r="G30" s="9">
+        <v>0</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="J30" s="7">
+        <v>102</v>
+      </c>
+      <c r="K30" s="14">
+        <f t="shared" si="0"/>
+        <v>102</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31" s="7">
+        <v>114.73684210526316</v>
+      </c>
+      <c r="F31" s="8">
+        <v>2</v>
+      </c>
+      <c r="G31" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="J31" s="7">
+        <v>109</v>
+      </c>
+      <c r="K31" s="14">
+        <f t="shared" si="0"/>
+        <v>109</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32" s="7">
+        <v>125</v>
+      </c>
+      <c r="F32" s="8">
+        <v>4</v>
+      </c>
+      <c r="G32" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J32" s="7">
+        <v>100</v>
+      </c>
+      <c r="K32" s="14">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E33" s="7">
+        <v>115.78947368421053</v>
+      </c>
+      <c r="F33" s="8">
+        <v>2</v>
+      </c>
+      <c r="G33" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J33" s="7">
+        <v>110</v>
+      </c>
+      <c r="K33" s="14">
+        <f t="shared" si="0"/>
+        <v>110</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="7">
+        <v>112.5</v>
+      </c>
+      <c r="F34" s="8">
+        <v>1</v>
+      </c>
+      <c r="G34" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J34" s="7">
+        <v>90</v>
+      </c>
+      <c r="K34" s="14">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="7">
+        <v>120</v>
+      </c>
+      <c r="F35" s="8">
+        <v>1</v>
+      </c>
+      <c r="G35" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="J35" s="7">
+        <v>96</v>
+      </c>
+      <c r="K35" s="14">
+        <f t="shared" si="0"/>
+        <v>96</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" s="7">
+        <v>110</v>
+      </c>
+      <c r="F36" s="8">
+        <v>4</v>
+      </c>
+      <c r="G36" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="J36" s="7">
+        <v>99</v>
+      </c>
+      <c r="K36" s="14">
+        <f t="shared" si="0"/>
+        <v>99</v>
+      </c>
+      <c r="L36" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37" s="7">
+        <v>100</v>
+      </c>
+      <c r="F37" s="8">
+        <v>1</v>
+      </c>
+      <c r="G37" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="J37" s="7">
+        <v>95</v>
+      </c>
+      <c r="K37" s="14">
+        <f t="shared" si="0"/>
+        <v>95</v>
+      </c>
+      <c r="L37" s="6"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E38" s="7">
+        <v>116.47058823529412</v>
+      </c>
+      <c r="F38" s="8">
+        <v>4</v>
+      </c>
+      <c r="G38" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="J38" s="7">
+        <v>99</v>
+      </c>
+      <c r="K38" s="14">
+        <f t="shared" si="0"/>
+        <v>99</v>
+      </c>
+      <c r="L38" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E39" s="7">
+        <v>110.52631578947368</v>
+      </c>
+      <c r="F39" s="8">
+        <v>1</v>
+      </c>
+      <c r="G39" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J39" s="7">
+        <v>105</v>
+      </c>
+      <c r="K39" s="14">
+        <f t="shared" si="0"/>
+        <v>105</v>
+      </c>
+      <c r="L39" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="7">
+        <v>74</v>
+      </c>
+      <c r="F40" s="8">
+        <v>2</v>
+      </c>
+      <c r="G40" s="9">
+        <v>0</v>
+      </c>
+      <c r="H40" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="F2" s="7">
-        <v>25</v>
-      </c>
-      <c r="G2" s="8">
+      <c r="J40" s="7">
+        <v>74</v>
+      </c>
+      <c r="K40" s="14">
+        <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+      <c r="L40" s="6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E41" s="7">
+        <v>115</v>
+      </c>
+      <c r="F41" s="8">
+        <v>1</v>
+      </c>
+      <c r="G41" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="J41" s="7">
+        <v>92</v>
+      </c>
+      <c r="K41" s="14">
+        <f t="shared" si="0"/>
+        <v>92</v>
+      </c>
+      <c r="L41" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" s="7">
+        <v>100</v>
+      </c>
+      <c r="F42" s="8">
+        <v>3</v>
+      </c>
+      <c r="G42" s="9">
         <v>0.15</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="H42" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="J42" s="7">
+        <v>85</v>
+      </c>
+      <c r="K42" s="14">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E43" s="7">
+        <v>135.55555555555554</v>
+      </c>
+      <c r="F43" s="8">
+        <v>2</v>
+      </c>
+      <c r="G43" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J43" s="7">
+        <v>122</v>
+      </c>
+      <c r="K43" s="14">
+        <f t="shared" si="0"/>
+        <v>121.99999999999999</v>
+      </c>
+      <c r="L43" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E44" s="7">
+        <v>108.23529411764706</v>
+      </c>
+      <c r="F44" s="8">
+        <v>2</v>
+      </c>
+      <c r="G44" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="J44" s="7">
+        <v>92</v>
+      </c>
+      <c r="K44" s="14">
+        <f t="shared" si="0"/>
+        <v>92</v>
+      </c>
+      <c r="L44" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="D45" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="E45" s="7">
+        <v>62.5</v>
+      </c>
+      <c r="F45" s="8">
+        <v>5</v>
+      </c>
+      <c r="G45" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="J45" s="7">
+        <v>50</v>
+      </c>
+      <c r="K45" s="14">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="L45" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="D46" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E46" s="7">
+        <v>105</v>
+      </c>
+      <c r="F46" s="8">
+        <v>2</v>
+      </c>
+      <c r="G46" s="9">
+        <v>0</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="J46" s="7">
+        <v>105</v>
+      </c>
+      <c r="K46" s="14">
+        <f t="shared" si="0"/>
+        <v>105</v>
+      </c>
+      <c r="L46" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" s="7">
+        <v>82.222222222222214</v>
+      </c>
+      <c r="F47" s="8">
+        <v>3</v>
+      </c>
+      <c r="G47" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="H47" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="F3" s="7">
-        <v>18</v>
-      </c>
-      <c r="G3" s="8">
+      <c r="J47" s="7">
+        <v>74</v>
+      </c>
+      <c r="K47" s="14">
+        <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+      <c r="L47" s="6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E48" s="7">
+        <v>98.82352941176471</v>
+      </c>
+      <c r="F48" s="8">
+        <v>1</v>
+      </c>
+      <c r="G48" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="J48" s="7">
+        <v>84</v>
+      </c>
+      <c r="K48" s="14">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49" s="7">
+        <v>117.64705882352942</v>
+      </c>
+      <c r="F49" s="8">
+        <v>2</v>
+      </c>
+      <c r="G49" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J49" s="7">
+        <v>100</v>
+      </c>
+      <c r="K49" s="14">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="L49" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="7">
+        <v>62.5</v>
+      </c>
+      <c r="F50" s="8">
+        <v>1</v>
+      </c>
+      <c r="G50" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="J50" s="7">
+        <v>50</v>
+      </c>
+      <c r="K50" s="14">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="L50" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" s="7">
+        <v>98.888888888888886</v>
+      </c>
+      <c r="F51" s="8">
+        <v>2</v>
+      </c>
+      <c r="G51" s="9">
         <v>0.1</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="6">
+      <c r="H51" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="F4" s="7">
-        <v>30</v>
-      </c>
-      <c r="G4" s="8">
+      <c r="J51" s="7">
+        <v>89</v>
+      </c>
+      <c r="K51" s="14">
+        <f t="shared" si="0"/>
+        <v>89</v>
+      </c>
+      <c r="L51" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E52" s="7">
+        <v>93.684210526315795</v>
+      </c>
+      <c r="F52" s="8">
+        <v>2</v>
+      </c>
+      <c r="G52" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="J52" s="7">
+        <v>89</v>
+      </c>
+      <c r="K52" s="14">
+        <f t="shared" si="0"/>
+        <v>89</v>
+      </c>
+      <c r="L52" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E53" s="7">
+        <v>61.05263157894737</v>
+      </c>
+      <c r="F53" s="8">
+        <v>3</v>
+      </c>
+      <c r="G53" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="J53" s="7">
+        <v>58</v>
+      </c>
+      <c r="K53" s="14">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="L53" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E54" s="7">
+        <v>82.10526315789474</v>
+      </c>
+      <c r="F54" s="8">
+        <v>2</v>
+      </c>
+      <c r="G54" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="J54" s="7">
+        <v>78</v>
+      </c>
+      <c r="K54" s="14">
+        <f t="shared" si="0"/>
+        <v>78</v>
+      </c>
+      <c r="L54" s="6" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E55" s="7">
+        <v>89</v>
+      </c>
+      <c r="F55" s="8">
+        <v>3</v>
+      </c>
+      <c r="G55" s="9">
         <v>0</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="6">
-        <v>92</v>
-      </c>
-      <c r="F5" s="7">
-        <v>12</v>
-      </c>
-      <c r="G5" s="8">
-        <v>0.05</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="6">
-        <v>75</v>
-      </c>
-      <c r="F6" s="7">
-        <v>40</v>
-      </c>
-      <c r="G6" s="8">
+      <c r="H55" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="J55" s="7">
+        <v>89</v>
+      </c>
+      <c r="K55" s="14">
+        <f t="shared" si="0"/>
+        <v>89</v>
+      </c>
+      <c r="L55" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E56" s="7">
+        <v>57.777777777777779</v>
+      </c>
+      <c r="F56" s="8">
+        <v>3</v>
+      </c>
+      <c r="G56" s="9">
         <v>0.1</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="6">
-        <v>98</v>
-      </c>
-      <c r="F7" s="7">
-        <v>15</v>
-      </c>
-      <c r="G7" s="8">
-        <v>0</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>34</v>
+      <c r="H56" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="J56" s="7">
+        <v>52</v>
+      </c>
+      <c r="K56" s="14">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="L56" s="6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" s="7">
+        <v>173.75</v>
+      </c>
+      <c r="F57" s="8">
+        <v>1</v>
+      </c>
+      <c r="G57" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="J57" s="7">
+        <v>139</v>
+      </c>
+      <c r="K57" s="14">
+        <f t="shared" si="0"/>
+        <v>139</v>
+      </c>
+      <c r="L57" s="6" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/catalogo_mikado.xlsx
+++ b/catalogo_mikado.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANDRE\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANDRE\Documents\Antigravity Proyectos\Mikado\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20700" windowHeight="7200"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12330" windowHeight="6930"/>
   </bookViews>
   <sheets>
     <sheet name="Catálogo Mikado Skincare" sheetId="1" r:id="rId1"/>
@@ -732,7 +732,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;S/&quot;\ #,##0.00"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -873,7 +873,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/catalogo_mikado.xlsx
+++ b/catalogo_mikado.xlsx
@@ -864,9 +864,6 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -874,6 +871,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1187,12 +1187,12 @@
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="17" customWidth="1"/>
     <col min="8" max="8" width="64.7109375" customWidth="1"/>
-    <col min="9" max="9" width="5.42578125" style="13" customWidth="1"/>
+    <col min="9" max="9" width="5.42578125" style="12" customWidth="1"/>
     <col min="10" max="10" width="20.42578125" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" style="11"/>
+    <col min="11" max="11" width="9.140625" style="10"/>
     <col min="12" max="12" width="19.85546875" customWidth="1"/>
-    <col min="13" max="13" width="15.5703125" style="11" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="11"/>
+    <col min="13" max="13" width="15.5703125" style="10" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1226,7 +1226,7 @@
       <c r="L1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="9" t="s">
         <v>232</v>
       </c>
       <c r="N1" s="2">
@@ -1248,13 +1248,14 @@
         <v>9</v>
       </c>
       <c r="E2" s="7">
-        <v>93.333333333333329</v>
+        <v>94</v>
       </c>
       <c r="F2" s="8">
         <v>2</v>
       </c>
-      <c r="G2" s="9">
-        <v>0.1</v>
+      <c r="G2" s="14">
+        <f>1-J2/E2</f>
+        <v>0.1063829787234043</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>10</v>
@@ -1262,7 +1263,7 @@
       <c r="J2" s="7">
         <v>84</v>
       </c>
-      <c r="K2" s="14">
+      <c r="K2" s="13">
         <f>E2*(1-G2)</f>
         <v>84</v>
       </c>
@@ -1289,8 +1290,9 @@
       <c r="F3" s="8">
         <v>2</v>
       </c>
-      <c r="G3" s="9">
-        <v>0.2</v>
+      <c r="G3" s="14">
+        <f t="shared" ref="G3:G57" si="0">1-J3/E3</f>
+        <v>0.19999999999999996</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>14</v>
@@ -1298,8 +1300,8 @@
       <c r="J3" s="7">
         <v>88</v>
       </c>
-      <c r="K3" s="14">
-        <f t="shared" ref="K3:K57" si="0">E3*(1-G3)</f>
+      <c r="K3" s="13">
+        <f t="shared" ref="K3:K57" si="1">E3*(1-G3)</f>
         <v>88</v>
       </c>
       <c r="L3" s="6" t="s">
@@ -1320,13 +1322,14 @@
         <v>16</v>
       </c>
       <c r="E4" s="7">
-        <v>98.888888888888886</v>
+        <v>99</v>
       </c>
       <c r="F4" s="8">
         <v>0</v>
       </c>
-      <c r="G4" s="9">
-        <v>0.1</v>
+      <c r="G4" s="14">
+        <f t="shared" si="0"/>
+        <v>0.10101010101010099</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>17</v>
@@ -1334,14 +1337,14 @@
       <c r="J4" s="7">
         <v>89</v>
       </c>
-      <c r="K4" s="14">
-        <f t="shared" si="0"/>
+      <c r="K4" s="13">
+        <f t="shared" si="1"/>
         <v>89</v>
       </c>
       <c r="L4" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="M4" s="12"/>
+      <c r="M4" s="11"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
@@ -1357,13 +1360,14 @@
         <v>13</v>
       </c>
       <c r="E5" s="7">
-        <v>102.22222222222221</v>
+        <v>102</v>
       </c>
       <c r="F5" s="8">
         <v>0</v>
       </c>
-      <c r="G5" s="9">
-        <v>0.1</v>
+      <c r="G5" s="14">
+        <f t="shared" si="0"/>
+        <v>9.8039215686274495E-2</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>19</v>
@@ -1371,8 +1375,8 @@
       <c r="J5" s="7">
         <v>92</v>
       </c>
-      <c r="K5" s="14">
-        <f t="shared" si="0"/>
+      <c r="K5" s="13">
+        <f t="shared" si="1"/>
         <v>92</v>
       </c>
       <c r="L5" s="6" t="s">
@@ -1398,7 +1402,8 @@
       <c r="F6" s="8">
         <v>0</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H6" s="5" t="s">
@@ -1407,8 +1412,8 @@
       <c r="J6" s="7">
         <v>75</v>
       </c>
-      <c r="K6" s="14">
-        <f t="shared" si="0"/>
+      <c r="K6" s="13">
+        <f t="shared" si="1"/>
         <v>75</v>
       </c>
       <c r="L6" s="6" t="s">
@@ -1434,7 +1439,8 @@
       <c r="F7" s="8">
         <v>2</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H7" s="5" t="s">
@@ -1443,8 +1449,8 @@
       <c r="J7" s="7">
         <v>99</v>
       </c>
-      <c r="K7" s="14">
-        <f t="shared" si="0"/>
+      <c r="K7" s="13">
+        <f t="shared" si="1"/>
         <v>99</v>
       </c>
       <c r="L7" s="6" t="s">
@@ -1465,13 +1471,14 @@
         <v>27</v>
       </c>
       <c r="E8" s="7">
-        <v>117.64705882352942</v>
+        <v>120</v>
       </c>
       <c r="F8" s="8">
         <v>1</v>
       </c>
-      <c r="G8" s="9">
-        <v>0.15</v>
+      <c r="G8" s="14">
+        <f t="shared" si="0"/>
+        <v>0.16666666666666663</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>28</v>
@@ -1479,8 +1486,8 @@
       <c r="J8" s="7">
         <v>100</v>
       </c>
-      <c r="K8" s="14">
-        <f t="shared" si="0"/>
+      <c r="K8" s="13">
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="L8" s="6" t="s">
@@ -1501,13 +1508,14 @@
         <v>27</v>
       </c>
       <c r="E9" s="7">
-        <v>111.11111111111111</v>
+        <v>110</v>
       </c>
       <c r="F9" s="8">
         <v>1</v>
       </c>
-      <c r="G9" s="9">
-        <v>0.1</v>
+      <c r="G9" s="14">
+        <f t="shared" si="0"/>
+        <v>9.0909090909090939E-2</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>29</v>
@@ -1515,8 +1523,8 @@
       <c r="J9" s="7">
         <v>100</v>
       </c>
-      <c r="K9" s="14">
-        <f t="shared" si="0"/>
+      <c r="K9" s="13">
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="L9" s="6" t="s">
@@ -1537,13 +1545,14 @@
         <v>13</v>
       </c>
       <c r="E10" s="7">
-        <v>123.75</v>
+        <v>125</v>
       </c>
       <c r="F10" s="8">
         <v>3</v>
       </c>
-      <c r="G10" s="9">
-        <v>0.2</v>
+      <c r="G10" s="14">
+        <f t="shared" si="0"/>
+        <v>0.20799999999999996</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>51</v>
@@ -1551,8 +1560,8 @@
       <c r="J10" s="7">
         <v>99</v>
       </c>
-      <c r="K10" s="14">
-        <f t="shared" si="0"/>
+      <c r="K10" s="13">
+        <f t="shared" si="1"/>
         <v>99</v>
       </c>
       <c r="L10" s="6" t="s">
@@ -1573,13 +1582,14 @@
         <v>44</v>
       </c>
       <c r="E11" s="7">
-        <v>88.421052631578945</v>
+        <v>90</v>
       </c>
       <c r="F11" s="8">
         <v>2</v>
       </c>
-      <c r="G11" s="9">
-        <v>0.05</v>
+      <c r="G11" s="14">
+        <f t="shared" si="0"/>
+        <v>6.6666666666666652E-2</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>52</v>
@@ -1587,8 +1597,8 @@
       <c r="J11" s="7">
         <v>84</v>
       </c>
-      <c r="K11" s="14">
-        <f t="shared" si="0"/>
+      <c r="K11" s="13">
+        <f t="shared" si="1"/>
         <v>84</v>
       </c>
       <c r="L11" s="6" t="s">
@@ -1609,13 +1619,14 @@
         <v>13</v>
       </c>
       <c r="E12" s="7">
-        <v>22.222222222222221</v>
+        <v>25</v>
       </c>
       <c r="F12" s="8">
         <v>2</v>
       </c>
-      <c r="G12" s="9">
-        <v>0.1</v>
+      <c r="G12" s="14">
+        <f t="shared" si="0"/>
+        <v>0.19999999999999996</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>53</v>
@@ -1623,8 +1634,8 @@
       <c r="J12" s="7">
         <v>20</v>
       </c>
-      <c r="K12" s="14">
-        <f t="shared" si="0"/>
+      <c r="K12" s="13">
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="L12" s="6" t="s">
@@ -1645,13 +1656,14 @@
         <v>9</v>
       </c>
       <c r="E13" s="7">
-        <v>96.842105263157904</v>
+        <v>100</v>
       </c>
       <c r="F13" s="8">
         <v>2</v>
       </c>
-      <c r="G13" s="9">
-        <v>0.05</v>
+      <c r="G13" s="14">
+        <f t="shared" si="0"/>
+        <v>7.999999999999996E-2</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>54</v>
@@ -1659,8 +1671,8 @@
       <c r="J13" s="7">
         <v>92</v>
       </c>
-      <c r="K13" s="14">
-        <f t="shared" si="0"/>
+      <c r="K13" s="13">
+        <f t="shared" si="1"/>
         <v>92</v>
       </c>
       <c r="L13" s="6" t="s">
@@ -1686,7 +1698,8 @@
       <c r="F14" s="8">
         <v>6</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H14" s="5" t="s">
@@ -1695,8 +1708,8 @@
       <c r="J14" s="7">
         <v>110</v>
       </c>
-      <c r="K14" s="14">
-        <f t="shared" si="0"/>
+      <c r="K14" s="13">
+        <f t="shared" si="1"/>
         <v>110</v>
       </c>
       <c r="L14" s="6"/>
@@ -1720,8 +1733,9 @@
       <c r="F15" s="8">
         <v>1</v>
       </c>
-      <c r="G15" s="9">
-        <v>0.1</v>
+      <c r="G15" s="14">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999978E-2</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>56</v>
@@ -1729,8 +1743,8 @@
       <c r="J15" s="7">
         <v>99</v>
       </c>
-      <c r="K15" s="14">
-        <f t="shared" si="0"/>
+      <c r="K15" s="13">
+        <f t="shared" si="1"/>
         <v>99</v>
       </c>
       <c r="L15" s="6" t="s">
@@ -1751,13 +1765,14 @@
         <v>24</v>
       </c>
       <c r="E16" s="7">
-        <v>104.21052631578948</v>
+        <v>105</v>
       </c>
       <c r="F16" s="8">
         <v>2</v>
       </c>
-      <c r="G16" s="9">
-        <v>0.05</v>
+      <c r="G16" s="14">
+        <f t="shared" si="0"/>
+        <v>5.7142857142857162E-2</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>57</v>
@@ -1765,8 +1780,8 @@
       <c r="J16" s="7">
         <v>99</v>
       </c>
-      <c r="K16" s="14">
-        <f t="shared" si="0"/>
+      <c r="K16" s="13">
+        <f t="shared" si="1"/>
         <v>99</v>
       </c>
       <c r="L16" s="6" t="s">
@@ -1787,13 +1802,14 @@
         <v>13</v>
       </c>
       <c r="E17" s="7">
-        <v>105.55555555555556</v>
+        <v>105</v>
       </c>
       <c r="F17" s="8">
         <v>1</v>
       </c>
-      <c r="G17" s="9">
-        <v>0.1</v>
+      <c r="G17" s="14">
+        <f t="shared" si="0"/>
+        <v>9.5238095238095233E-2</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>58</v>
@@ -1801,8 +1817,8 @@
       <c r="J17" s="7">
         <v>95</v>
       </c>
-      <c r="K17" s="14">
-        <f t="shared" si="0"/>
+      <c r="K17" s="13">
+        <f t="shared" si="1"/>
         <v>95</v>
       </c>
       <c r="L17" s="6" t="s">
@@ -1828,7 +1844,8 @@
       <c r="F18" s="8">
         <v>2</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H18" s="5" t="s">
@@ -1837,8 +1854,8 @@
       <c r="J18" s="7">
         <v>92</v>
       </c>
-      <c r="K18" s="14">
-        <f t="shared" si="0"/>
+      <c r="K18" s="13">
+        <f t="shared" si="1"/>
         <v>92</v>
       </c>
       <c r="L18" s="6" t="s">
@@ -1859,13 +1876,14 @@
         <v>45</v>
       </c>
       <c r="E19" s="7">
-        <v>123.75</v>
+        <v>125</v>
       </c>
       <c r="F19" s="8">
         <v>6</v>
       </c>
-      <c r="G19" s="9">
-        <v>0.2</v>
+      <c r="G19" s="14">
+        <f t="shared" si="0"/>
+        <v>0.20799999999999996</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>60</v>
@@ -1873,8 +1891,8 @@
       <c r="J19" s="7">
         <v>99</v>
       </c>
-      <c r="K19" s="14">
-        <f t="shared" si="0"/>
+      <c r="K19" s="13">
+        <f t="shared" si="1"/>
         <v>99</v>
       </c>
       <c r="L19" s="6" t="s">
@@ -1895,13 +1913,14 @@
         <v>13</v>
       </c>
       <c r="E20" s="7">
-        <v>141.1764705882353</v>
+        <v>140</v>
       </c>
       <c r="F20" s="8">
         <v>3</v>
       </c>
-      <c r="G20" s="9">
-        <v>0.15</v>
+      <c r="G20" s="14">
+        <f t="shared" si="0"/>
+        <v>0.1428571428571429</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>61</v>
@@ -1909,8 +1928,8 @@
       <c r="J20" s="7">
         <v>120</v>
       </c>
-      <c r="K20" s="14">
-        <f t="shared" si="0"/>
+      <c r="K20" s="13">
+        <f t="shared" si="1"/>
         <v>120</v>
       </c>
       <c r="L20" s="6" t="s">
@@ -1931,13 +1950,14 @@
         <v>13</v>
       </c>
       <c r="E21" s="7">
-        <v>108.23529411764706</v>
+        <v>110</v>
       </c>
       <c r="F21" s="8">
         <v>1</v>
       </c>
-      <c r="G21" s="9">
-        <v>0.15</v>
+      <c r="G21" s="14">
+        <f t="shared" si="0"/>
+        <v>0.16363636363636369</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>61</v>
@@ -1945,8 +1965,8 @@
       <c r="J21" s="7">
         <v>92</v>
       </c>
-      <c r="K21" s="14">
-        <f t="shared" si="0"/>
+      <c r="K21" s="13">
+        <f t="shared" si="1"/>
         <v>92</v>
       </c>
       <c r="L21" s="6" t="s">
@@ -1967,13 +1987,14 @@
         <v>13</v>
       </c>
       <c r="E22" s="7">
-        <v>131.25</v>
+        <v>130</v>
       </c>
       <c r="F22" s="8">
         <v>1</v>
       </c>
-      <c r="G22" s="9">
-        <v>0.2</v>
+      <c r="G22" s="14">
+        <f t="shared" si="0"/>
+        <v>0.19230769230769229</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>61</v>
@@ -1981,8 +2002,8 @@
       <c r="J22" s="7">
         <v>105</v>
       </c>
-      <c r="K22" s="14">
-        <f t="shared" si="0"/>
+      <c r="K22" s="13">
+        <f t="shared" si="1"/>
         <v>105</v>
       </c>
       <c r="L22" s="6" t="s">
@@ -2008,7 +2029,8 @@
       <c r="F23" s="8">
         <v>4</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G23" s="14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H23" s="5" t="s">
@@ -2017,8 +2039,8 @@
       <c r="J23" s="7">
         <v>100</v>
       </c>
-      <c r="K23" s="14">
-        <f t="shared" si="0"/>
+      <c r="K23" s="13">
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="L23" s="6" t="s">
@@ -2039,13 +2061,14 @@
         <v>16</v>
       </c>
       <c r="E24" s="7">
-        <v>121.11111111111111</v>
+        <v>119</v>
       </c>
       <c r="F24" s="8">
         <v>1</v>
       </c>
-      <c r="G24" s="9">
-        <v>0.1</v>
+      <c r="G24" s="14">
+        <f t="shared" si="0"/>
+        <v>8.4033613445378186E-2</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>63</v>
@@ -2053,8 +2076,8 @@
       <c r="J24" s="7">
         <v>109</v>
       </c>
-      <c r="K24" s="14">
-        <f t="shared" si="0"/>
+      <c r="K24" s="13">
+        <f t="shared" si="1"/>
         <v>109</v>
       </c>
       <c r="L24" s="6" t="s">
@@ -2080,7 +2103,8 @@
       <c r="F25" s="8">
         <v>1</v>
       </c>
-      <c r="G25" s="9">
+      <c r="G25" s="14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H25" s="5" t="s">
@@ -2089,8 +2113,8 @@
       <c r="J25" s="7">
         <v>128</v>
       </c>
-      <c r="K25" s="14">
-        <f t="shared" si="0"/>
+      <c r="K25" s="13">
+        <f t="shared" si="1"/>
         <v>128</v>
       </c>
       <c r="L25" s="6" t="s">
@@ -2111,13 +2135,14 @@
         <v>21</v>
       </c>
       <c r="E26" s="7">
-        <v>25.882352941176471</v>
+        <v>26</v>
       </c>
       <c r="F26" s="8">
         <v>2</v>
       </c>
-      <c r="G26" s="9">
-        <v>0.15</v>
+      <c r="G26" s="14">
+        <f t="shared" si="0"/>
+        <v>0.15384615384615385</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>65</v>
@@ -2125,8 +2150,8 @@
       <c r="J26" s="7">
         <v>22</v>
       </c>
-      <c r="K26" s="14">
-        <f t="shared" si="0"/>
+      <c r="K26" s="13">
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="L26" s="6" t="s">
@@ -2152,7 +2177,8 @@
       <c r="F27" s="8">
         <v>1</v>
       </c>
-      <c r="G27" s="9">
+      <c r="G27" s="14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H27" s="5" t="s">
@@ -2161,8 +2187,8 @@
       <c r="J27" s="7">
         <v>109</v>
       </c>
-      <c r="K27" s="14">
-        <f t="shared" si="0"/>
+      <c r="K27" s="13">
+        <f t="shared" si="1"/>
         <v>109</v>
       </c>
       <c r="L27" s="6" t="s">
@@ -2188,7 +2214,8 @@
       <c r="F28" s="8">
         <v>2</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G28" s="14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H28" s="5" t="s">
@@ -2197,8 +2224,8 @@
       <c r="J28" s="7">
         <v>109</v>
       </c>
-      <c r="K28" s="14">
-        <f t="shared" si="0"/>
+      <c r="K28" s="13">
+        <f t="shared" si="1"/>
         <v>109</v>
       </c>
       <c r="L28" s="6" t="s">
@@ -2224,8 +2251,9 @@
       <c r="F29" s="8">
         <v>10</v>
       </c>
-      <c r="G29" s="9">
-        <v>0.2</v>
+      <c r="G29" s="14">
+        <f t="shared" si="0"/>
+        <v>0.19999999999999996</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>68</v>
@@ -2233,8 +2261,8 @@
       <c r="J29" s="7">
         <v>20</v>
       </c>
-      <c r="K29" s="14">
-        <f t="shared" si="0"/>
+      <c r="K29" s="13">
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="L29" s="6"/>
@@ -2258,7 +2286,8 @@
       <c r="F30" s="8">
         <v>1</v>
       </c>
-      <c r="G30" s="9">
+      <c r="G30" s="14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H30" s="5" t="s">
@@ -2267,8 +2296,8 @@
       <c r="J30" s="7">
         <v>102</v>
       </c>
-      <c r="K30" s="14">
-        <f t="shared" si="0"/>
+      <c r="K30" s="13">
+        <f t="shared" si="1"/>
         <v>102</v>
       </c>
       <c r="L30" s="6" t="s">
@@ -2289,13 +2318,14 @@
         <v>46</v>
       </c>
       <c r="E31" s="7">
-        <v>114.73684210526316</v>
+        <v>120</v>
       </c>
       <c r="F31" s="8">
         <v>2</v>
       </c>
-      <c r="G31" s="9">
-        <v>0.05</v>
+      <c r="G31" s="14">
+        <f t="shared" si="0"/>
+        <v>9.1666666666666674E-2</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>70</v>
@@ -2303,8 +2333,8 @@
       <c r="J31" s="7">
         <v>109</v>
       </c>
-      <c r="K31" s="14">
-        <f t="shared" si="0"/>
+      <c r="K31" s="13">
+        <f t="shared" si="1"/>
         <v>109</v>
       </c>
       <c r="L31" s="6" t="s">
@@ -2330,8 +2360,9 @@
       <c r="F32" s="8">
         <v>4</v>
       </c>
-      <c r="G32" s="9">
-        <v>0.2</v>
+      <c r="G32" s="14">
+        <f t="shared" si="0"/>
+        <v>0.19999999999999996</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>71</v>
@@ -2339,8 +2370,8 @@
       <c r="J32" s="7">
         <v>100</v>
       </c>
-      <c r="K32" s="14">
-        <f t="shared" si="0"/>
+      <c r="K32" s="13">
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="L32" s="6" t="s">
@@ -2361,13 +2392,14 @@
         <v>46</v>
       </c>
       <c r="E33" s="7">
-        <v>115.78947368421053</v>
+        <v>115</v>
       </c>
       <c r="F33" s="8">
         <v>2</v>
       </c>
-      <c r="G33" s="9">
-        <v>0.05</v>
+      <c r="G33" s="14">
+        <f t="shared" si="0"/>
+        <v>4.3478260869565188E-2</v>
       </c>
       <c r="H33" s="5" t="s">
         <v>72</v>
@@ -2375,8 +2407,8 @@
       <c r="J33" s="7">
         <v>110</v>
       </c>
-      <c r="K33" s="14">
-        <f t="shared" si="0"/>
+      <c r="K33" s="13">
+        <f t="shared" si="1"/>
         <v>110</v>
       </c>
       <c r="L33" s="6" t="s">
@@ -2397,13 +2429,14 @@
         <v>13</v>
       </c>
       <c r="E34" s="7">
-        <v>112.5</v>
+        <v>110</v>
       </c>
       <c r="F34" s="8">
         <v>1</v>
       </c>
-      <c r="G34" s="9">
-        <v>0.2</v>
+      <c r="G34" s="14">
+        <f t="shared" si="0"/>
+        <v>0.18181818181818177</v>
       </c>
       <c r="H34" s="5" t="s">
         <v>73</v>
@@ -2411,8 +2444,8 @@
       <c r="J34" s="7">
         <v>90</v>
       </c>
-      <c r="K34" s="14">
-        <f t="shared" si="0"/>
+      <c r="K34" s="13">
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="L34" s="6" t="s">
@@ -2438,8 +2471,9 @@
       <c r="F35" s="8">
         <v>1</v>
       </c>
-      <c r="G35" s="9">
-        <v>0.2</v>
+      <c r="G35" s="14">
+        <f t="shared" si="0"/>
+        <v>0.19999999999999996</v>
       </c>
       <c r="H35" s="5" t="s">
         <v>74</v>
@@ -2447,8 +2481,8 @@
       <c r="J35" s="7">
         <v>96</v>
       </c>
-      <c r="K35" s="14">
-        <f t="shared" si="0"/>
+      <c r="K35" s="13">
+        <f t="shared" si="1"/>
         <v>96</v>
       </c>
       <c r="L35" s="6" t="s">
@@ -2474,8 +2508,9 @@
       <c r="F36" s="8">
         <v>4</v>
       </c>
-      <c r="G36" s="9">
-        <v>0.1</v>
+      <c r="G36" s="14">
+        <f t="shared" si="0"/>
+        <v>9.9999999999999978E-2</v>
       </c>
       <c r="H36" s="5" t="s">
         <v>75</v>
@@ -2483,8 +2518,8 @@
       <c r="J36" s="7">
         <v>99</v>
       </c>
-      <c r="K36" s="14">
-        <f t="shared" si="0"/>
+      <c r="K36" s="13">
+        <f t="shared" si="1"/>
         <v>99</v>
       </c>
       <c r="L36" s="6" t="s">
@@ -2505,13 +2540,14 @@
         <v>9</v>
       </c>
       <c r="E37" s="7">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F37" s="8">
         <v>1</v>
       </c>
-      <c r="G37" s="9">
-        <v>0.05</v>
+      <c r="G37" s="14">
+        <f t="shared" si="0"/>
+        <v>9.5238095238095233E-2</v>
       </c>
       <c r="H37" s="5" t="s">
         <v>76</v>
@@ -2519,8 +2555,8 @@
       <c r="J37" s="7">
         <v>95</v>
       </c>
-      <c r="K37" s="14">
-        <f t="shared" si="0"/>
+      <c r="K37" s="13">
+        <f t="shared" si="1"/>
         <v>95</v>
       </c>
       <c r="L37" s="6"/>
@@ -2539,13 +2575,14 @@
         <v>44</v>
       </c>
       <c r="E38" s="7">
-        <v>116.47058823529412</v>
+        <v>120</v>
       </c>
       <c r="F38" s="8">
         <v>4</v>
       </c>
-      <c r="G38" s="9">
-        <v>0.15</v>
+      <c r="G38" s="14">
+        <f t="shared" si="0"/>
+        <v>0.17500000000000004</v>
       </c>
       <c r="H38" s="5" t="s">
         <v>77</v>
@@ -2553,8 +2590,8 @@
       <c r="J38" s="7">
         <v>99</v>
       </c>
-      <c r="K38" s="14">
-        <f t="shared" si="0"/>
+      <c r="K38" s="13">
+        <f t="shared" si="1"/>
         <v>99</v>
       </c>
       <c r="L38" s="6" t="s">
@@ -2575,13 +2612,14 @@
         <v>45</v>
       </c>
       <c r="E39" s="7">
-        <v>110.52631578947368</v>
+        <v>115</v>
       </c>
       <c r="F39" s="8">
         <v>1</v>
       </c>
-      <c r="G39" s="9">
-        <v>0.05</v>
+      <c r="G39" s="14">
+        <f t="shared" si="0"/>
+        <v>8.6956521739130488E-2</v>
       </c>
       <c r="H39" s="5" t="s">
         <v>78</v>
@@ -2589,8 +2627,8 @@
       <c r="J39" s="7">
         <v>105</v>
       </c>
-      <c r="K39" s="14">
-        <f t="shared" si="0"/>
+      <c r="K39" s="13">
+        <f t="shared" si="1"/>
         <v>105</v>
       </c>
       <c r="L39" s="6" t="s">
@@ -2616,7 +2654,8 @@
       <c r="F40" s="8">
         <v>2</v>
       </c>
-      <c r="G40" s="9">
+      <c r="G40" s="14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H40" s="5" t="s">
@@ -2625,8 +2664,8 @@
       <c r="J40" s="7">
         <v>74</v>
       </c>
-      <c r="K40" s="14">
-        <f t="shared" si="0"/>
+      <c r="K40" s="13">
+        <f t="shared" si="1"/>
         <v>74</v>
       </c>
       <c r="L40" s="6" t="s">
@@ -2652,8 +2691,9 @@
       <c r="F41" s="8">
         <v>1</v>
       </c>
-      <c r="G41" s="9">
-        <v>0.2</v>
+      <c r="G41" s="14">
+        <f t="shared" si="0"/>
+        <v>0.19999999999999996</v>
       </c>
       <c r="H41" s="5" t="s">
         <v>80</v>
@@ -2661,8 +2701,8 @@
       <c r="J41" s="7">
         <v>92</v>
       </c>
-      <c r="K41" s="14">
-        <f t="shared" si="0"/>
+      <c r="K41" s="13">
+        <f t="shared" si="1"/>
         <v>92</v>
       </c>
       <c r="L41" s="6" t="s">
@@ -2688,8 +2728,9 @@
       <c r="F42" s="8">
         <v>3</v>
       </c>
-      <c r="G42" s="9">
-        <v>0.15</v>
+      <c r="G42" s="14">
+        <f t="shared" si="0"/>
+        <v>0.15000000000000002</v>
       </c>
       <c r="H42" s="5" t="s">
         <v>81</v>
@@ -2697,8 +2738,8 @@
       <c r="J42" s="7">
         <v>85</v>
       </c>
-      <c r="K42" s="14">
-        <f t="shared" si="0"/>
+      <c r="K42" s="13">
+        <f t="shared" si="1"/>
         <v>85</v>
       </c>
       <c r="L42" s="6" t="s">
@@ -2719,13 +2760,14 @@
         <v>47</v>
       </c>
       <c r="E43" s="7">
-        <v>135.55555555555554</v>
+        <v>135</v>
       </c>
       <c r="F43" s="8">
         <v>2</v>
       </c>
-      <c r="G43" s="9">
-        <v>0.1</v>
+      <c r="G43" s="14">
+        <f t="shared" si="0"/>
+        <v>9.6296296296296324E-2</v>
       </c>
       <c r="H43" s="5" t="s">
         <v>50</v>
@@ -2733,9 +2775,9 @@
       <c r="J43" s="7">
         <v>122</v>
       </c>
-      <c r="K43" s="14">
-        <f t="shared" si="0"/>
-        <v>121.99999999999999</v>
+      <c r="K43" s="13">
+        <f t="shared" si="1"/>
+        <v>122</v>
       </c>
       <c r="L43" s="6" t="s">
         <v>117</v>
@@ -2755,13 +2797,14 @@
         <v>46</v>
       </c>
       <c r="E44" s="7">
-        <v>108.23529411764706</v>
+        <v>110</v>
       </c>
       <c r="F44" s="8">
         <v>2</v>
       </c>
-      <c r="G44" s="9">
-        <v>0.15</v>
+      <c r="G44" s="14">
+        <f t="shared" si="0"/>
+        <v>0.16363636363636369</v>
       </c>
       <c r="H44" s="5" t="s">
         <v>82</v>
@@ -2769,8 +2812,8 @@
       <c r="J44" s="7">
         <v>92</v>
       </c>
-      <c r="K44" s="14">
-        <f t="shared" si="0"/>
+      <c r="K44" s="13">
+        <f t="shared" si="1"/>
         <v>92</v>
       </c>
       <c r="L44" s="6" t="s">
@@ -2796,8 +2839,9 @@
       <c r="F45" s="8">
         <v>5</v>
       </c>
-      <c r="G45" s="9">
-        <v>0.2</v>
+      <c r="G45" s="14">
+        <f t="shared" si="0"/>
+        <v>0.19999999999999996</v>
       </c>
       <c r="H45" s="5" t="s">
         <v>83</v>
@@ -2805,8 +2849,8 @@
       <c r="J45" s="7">
         <v>50</v>
       </c>
-      <c r="K45" s="14">
-        <f t="shared" si="0"/>
+      <c r="K45" s="13">
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="L45" s="6" t="s">
@@ -2832,7 +2876,8 @@
       <c r="F46" s="8">
         <v>2</v>
       </c>
-      <c r="G46" s="9">
+      <c r="G46" s="14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H46" s="5" t="s">
@@ -2841,8 +2886,8 @@
       <c r="J46" s="7">
         <v>105</v>
       </c>
-      <c r="K46" s="14">
-        <f t="shared" si="0"/>
+      <c r="K46" s="13">
+        <f t="shared" si="1"/>
         <v>105</v>
       </c>
       <c r="L46" s="6" t="s">
@@ -2863,13 +2908,14 @@
         <v>24</v>
       </c>
       <c r="E47" s="7">
-        <v>82.222222222222214</v>
+        <v>82</v>
       </c>
       <c r="F47" s="8">
         <v>3</v>
       </c>
-      <c r="G47" s="9">
-        <v>0.1</v>
+      <c r="G47" s="14">
+        <f t="shared" si="0"/>
+        <v>9.7560975609756073E-2</v>
       </c>
       <c r="H47" s="5" t="s">
         <v>85</v>
@@ -2877,8 +2923,8 @@
       <c r="J47" s="7">
         <v>74</v>
       </c>
-      <c r="K47" s="14">
-        <f t="shared" si="0"/>
+      <c r="K47" s="13">
+        <f t="shared" si="1"/>
         <v>74</v>
       </c>
       <c r="L47" s="6" t="s">
@@ -2899,13 +2945,14 @@
         <v>44</v>
       </c>
       <c r="E48" s="7">
-        <v>98.82352941176471</v>
+        <v>99</v>
       </c>
       <c r="F48" s="8">
         <v>1</v>
       </c>
-      <c r="G48" s="9">
-        <v>0.15</v>
+      <c r="G48" s="14">
+        <f t="shared" si="0"/>
+        <v>0.15151515151515149</v>
       </c>
       <c r="H48" s="5" t="s">
         <v>86</v>
@@ -2913,8 +2960,8 @@
       <c r="J48" s="7">
         <v>84</v>
       </c>
-      <c r="K48" s="14">
-        <f t="shared" si="0"/>
+      <c r="K48" s="13">
+        <f t="shared" si="1"/>
         <v>84</v>
       </c>
       <c r="L48" s="6" t="s">
@@ -2935,13 +2982,14 @@
         <v>16</v>
       </c>
       <c r="E49" s="7">
-        <v>117.64705882352942</v>
+        <v>115</v>
       </c>
       <c r="F49" s="8">
         <v>2</v>
       </c>
-      <c r="G49" s="9">
-        <v>0.15</v>
+      <c r="G49" s="14">
+        <f t="shared" si="0"/>
+        <v>0.13043478260869568</v>
       </c>
       <c r="H49" s="5" t="s">
         <v>87</v>
@@ -2949,8 +2997,8 @@
       <c r="J49" s="7">
         <v>100</v>
       </c>
-      <c r="K49" s="14">
-        <f t="shared" si="0"/>
+      <c r="K49" s="13">
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="L49" s="6" t="s">
@@ -2976,8 +3024,9 @@
       <c r="F50" s="8">
         <v>1</v>
       </c>
-      <c r="G50" s="9">
-        <v>0.2</v>
+      <c r="G50" s="14">
+        <f t="shared" si="0"/>
+        <v>0.19999999999999996</v>
       </c>
       <c r="H50" s="5" t="s">
         <v>88</v>
@@ -2985,8 +3034,8 @@
       <c r="J50" s="7">
         <v>50</v>
       </c>
-      <c r="K50" s="14">
-        <f t="shared" si="0"/>
+      <c r="K50" s="13">
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="L50" s="6" t="s">
@@ -3007,13 +3056,14 @@
         <v>9</v>
       </c>
       <c r="E51" s="7">
-        <v>98.888888888888886</v>
+        <v>99</v>
       </c>
       <c r="F51" s="8">
         <v>2</v>
       </c>
-      <c r="G51" s="9">
-        <v>0.1</v>
+      <c r="G51" s="14">
+        <f t="shared" si="0"/>
+        <v>0.10101010101010099</v>
       </c>
       <c r="H51" s="5" t="s">
         <v>89</v>
@@ -3021,8 +3071,8 @@
       <c r="J51" s="7">
         <v>89</v>
       </c>
-      <c r="K51" s="14">
-        <f t="shared" si="0"/>
+      <c r="K51" s="13">
+        <f t="shared" si="1"/>
         <v>89</v>
       </c>
       <c r="L51" s="6" t="s">
@@ -3043,13 +3093,14 @@
         <v>9</v>
       </c>
       <c r="E52" s="7">
-        <v>93.684210526315795</v>
+        <v>99</v>
       </c>
       <c r="F52" s="8">
         <v>2</v>
       </c>
-      <c r="G52" s="9">
-        <v>0.05</v>
+      <c r="G52" s="14">
+        <f t="shared" si="0"/>
+        <v>0.10101010101010099</v>
       </c>
       <c r="H52" s="5" t="s">
         <v>90</v>
@@ -3057,8 +3108,8 @@
       <c r="J52" s="7">
         <v>89</v>
       </c>
-      <c r="K52" s="14">
-        <f t="shared" si="0"/>
+      <c r="K52" s="13">
+        <f t="shared" si="1"/>
         <v>89</v>
       </c>
       <c r="L52" s="6" t="s">
@@ -3079,13 +3130,14 @@
         <v>43</v>
       </c>
       <c r="E53" s="7">
-        <v>61.05263157894737</v>
+        <v>65</v>
       </c>
       <c r="F53" s="8">
         <v>3</v>
       </c>
-      <c r="G53" s="9">
-        <v>0.05</v>
+      <c r="G53" s="14">
+        <f t="shared" si="0"/>
+        <v>0.10769230769230764</v>
       </c>
       <c r="H53" s="5" t="s">
         <v>91</v>
@@ -3093,8 +3145,8 @@
       <c r="J53" s="7">
         <v>58</v>
       </c>
-      <c r="K53" s="14">
-        <f t="shared" si="0"/>
+      <c r="K53" s="13">
+        <f t="shared" si="1"/>
         <v>58</v>
       </c>
       <c r="L53" s="6" t="s">
@@ -3115,13 +3167,14 @@
         <v>24</v>
       </c>
       <c r="E54" s="7">
-        <v>82.10526315789474</v>
+        <v>85</v>
       </c>
       <c r="F54" s="8">
         <v>2</v>
       </c>
-      <c r="G54" s="9">
-        <v>0.05</v>
+      <c r="G54" s="14">
+        <f t="shared" si="0"/>
+        <v>8.2352941176470629E-2</v>
       </c>
       <c r="H54" s="5" t="s">
         <v>92</v>
@@ -3129,8 +3182,8 @@
       <c r="J54" s="7">
         <v>78</v>
       </c>
-      <c r="K54" s="14">
-        <f t="shared" si="0"/>
+      <c r="K54" s="13">
+        <f t="shared" si="1"/>
         <v>78</v>
       </c>
       <c r="L54" s="6" t="s">
@@ -3156,7 +3209,8 @@
       <c r="F55" s="8">
         <v>3</v>
       </c>
-      <c r="G55" s="9">
+      <c r="G55" s="14">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H55" s="5" t="s">
@@ -3165,8 +3219,8 @@
       <c r="J55" s="7">
         <v>89</v>
       </c>
-      <c r="K55" s="14">
-        <f t="shared" si="0"/>
+      <c r="K55" s="13">
+        <f t="shared" si="1"/>
         <v>89</v>
       </c>
       <c r="L55" s="6" t="s">
@@ -3187,13 +3241,14 @@
         <v>43</v>
       </c>
       <c r="E56" s="7">
-        <v>57.777777777777779</v>
+        <v>58</v>
       </c>
       <c r="F56" s="8">
         <v>3</v>
       </c>
-      <c r="G56" s="9">
-        <v>0.1</v>
+      <c r="G56" s="14">
+        <f t="shared" si="0"/>
+        <v>0.10344827586206895</v>
       </c>
       <c r="H56" s="5" t="s">
         <v>95</v>
@@ -3201,8 +3256,8 @@
       <c r="J56" s="7">
         <v>52</v>
       </c>
-      <c r="K56" s="14">
-        <f t="shared" si="0"/>
+      <c r="K56" s="13">
+        <f t="shared" si="1"/>
         <v>52</v>
       </c>
       <c r="L56" s="6" t="s">
@@ -3223,13 +3278,14 @@
         <v>9</v>
       </c>
       <c r="E57" s="7">
-        <v>173.75</v>
+        <v>169</v>
       </c>
       <c r="F57" s="8">
         <v>1</v>
       </c>
-      <c r="G57" s="9">
-        <v>0.2</v>
+      <c r="G57" s="14">
+        <f t="shared" si="0"/>
+        <v>0.1775147928994083</v>
       </c>
       <c r="H57" s="5" t="s">
         <v>93</v>
@@ -3237,8 +3293,8 @@
       <c r="J57" s="7">
         <v>139</v>
       </c>
-      <c r="K57" s="14">
-        <f t="shared" si="0"/>
+      <c r="K57" s="13">
+        <f t="shared" si="1"/>
         <v>139</v>
       </c>
       <c r="L57" s="6" t="s">

--- a/catalogo_mikado.xlsx
+++ b/catalogo_mikado.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="233">
   <si>
     <t>Codigo</t>
   </si>
@@ -156,12 +156,6 @@
     <t>Make up</t>
   </si>
   <si>
-    <t>Eye Cream</t>
-  </si>
-  <si>
-    <t>Booster</t>
-  </si>
-  <si>
     <t>Hidratante</t>
   </si>
   <si>
@@ -724,6 +718,9 @@
   </si>
   <si>
     <t>I'M FROM</t>
+  </si>
+  <si>
+    <t>Contorno de Ojos</t>
   </si>
 </sst>
 </file>
@@ -1182,7 +1179,7 @@
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="21.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="74.140625" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="17" customWidth="1"/>
@@ -1221,13 +1218,13 @@
         <v>7</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="N1" s="2">
         <f>SUM(F2:F937)</f>
@@ -1239,10 +1236,10 @@
         <v>8</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>9</v>
@@ -1268,7 +1265,7 @@
         <v>84</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -1279,7 +1276,7 @@
         <v>12</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>13</v>
@@ -1305,7 +1302,7 @@
         <v>88</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -1313,10 +1310,10 @@
         <v>15</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>16</v>
@@ -1342,7 +1339,7 @@
         <v>89</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="M4" s="11"/>
     </row>
@@ -1354,7 +1351,7 @@
         <v>40</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>13</v>
@@ -1380,7 +1377,7 @@
         <v>92</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -1388,10 +1385,10 @@
         <v>20</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>21</v>
@@ -1417,7 +1414,7 @@
         <v>75</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -1428,7 +1425,7 @@
         <v>40</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>24</v>
@@ -1454,18 +1451,18 @@
         <v>99</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>27</v>
@@ -1491,18 +1488,18 @@
         <v>100</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>27</v>
@@ -1528,18 +1525,18 @@
         <v>100</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>13</v>
@@ -1555,7 +1552,7 @@
         <v>0.20799999999999996</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J10" s="7">
         <v>99</v>
@@ -1565,21 +1562,21 @@
         <v>99</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>44</v>
+        <v>232</v>
       </c>
       <c r="E11" s="7">
         <v>90</v>
@@ -1592,7 +1589,7 @@
         <v>6.6666666666666652E-2</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J11" s="7">
         <v>84</v>
@@ -1602,18 +1599,18 @@
         <v>84</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>13</v>
@@ -1629,7 +1626,7 @@
         <v>0.19999999999999996</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J12" s="7">
         <v>20</v>
@@ -1639,18 +1636,18 @@
         <v>20</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>9</v>
@@ -1666,7 +1663,7 @@
         <v>7.999999999999996E-2</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J13" s="7">
         <v>92</v>
@@ -1676,21 +1673,21 @@
         <v>92</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E14" s="7">
         <v>110</v>
@@ -1703,7 +1700,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J14" s="7">
         <v>110</v>
@@ -1716,13 +1713,13 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>24</v>
@@ -1738,7 +1735,7 @@
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J15" s="7">
         <v>99</v>
@@ -1748,18 +1745,18 @@
         <v>99</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>24</v>
@@ -1775,7 +1772,7 @@
         <v>5.7142857142857162E-2</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J16" s="7">
         <v>99</v>
@@ -1785,18 +1782,18 @@
         <v>99</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>13</v>
@@ -1812,7 +1809,7 @@
         <v>9.5238095238095233E-2</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J17" s="7">
         <v>95</v>
@@ -1822,18 +1819,18 @@
         <v>95</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>9</v>
@@ -1849,7 +1846,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J18" s="7">
         <v>92</v>
@@ -1859,21 +1856,21 @@
         <v>92</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>45</v>
+        <v>232</v>
       </c>
       <c r="E19" s="7">
         <v>125</v>
@@ -1886,7 +1883,7 @@
         <v>0.20799999999999996</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J19" s="7">
         <v>99</v>
@@ -1896,18 +1893,18 @@
         <v>99</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>13</v>
@@ -1923,7 +1920,7 @@
         <v>0.1428571428571429</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J20" s="7">
         <v>120</v>
@@ -1933,18 +1930,18 @@
         <v>120</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>13</v>
@@ -1960,7 +1957,7 @@
         <v>0.16363636363636369</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J21" s="7">
         <v>92</v>
@@ -1970,18 +1967,18 @@
         <v>92</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>13</v>
@@ -1997,7 +1994,7 @@
         <v>0.19230769230769229</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J22" s="7">
         <v>105</v>
@@ -2007,21 +2004,21 @@
         <v>105</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E23" s="7">
         <v>100</v>
@@ -2034,7 +2031,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J23" s="7">
         <v>100</v>
@@ -2044,18 +2041,18 @@
         <v>100</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>16</v>
@@ -2071,7 +2068,7 @@
         <v>8.4033613445378186E-2</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J24" s="7">
         <v>109</v>
@@ -2081,18 +2078,18 @@
         <v>109</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>33</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>21</v>
@@ -2108,7 +2105,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J25" s="7">
         <v>128</v>
@@ -2118,18 +2115,18 @@
         <v>128</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>21</v>
@@ -2145,7 +2142,7 @@
         <v>0.15384615384615385</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J26" s="7">
         <v>22</v>
@@ -2155,18 +2152,18 @@
         <v>22</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>21</v>
@@ -2182,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J27" s="7">
         <v>109</v>
@@ -2192,21 +2189,21 @@
         <v>109</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E28" s="7">
         <v>109</v>
@@ -2219,7 +2216,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J28" s="7">
         <v>109</v>
@@ -2229,21 +2226,21 @@
         <v>109</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E29" s="7">
         <v>25</v>
@@ -2256,7 +2253,7 @@
         <v>0.19999999999999996</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J29" s="7">
         <v>20</v>
@@ -2269,13 +2266,13 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>24</v>
@@ -2291,7 +2288,7 @@
         <v>0</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J30" s="7">
         <v>102</v>
@@ -2301,21 +2298,21 @@
         <v>102</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E31" s="7">
         <v>120</v>
@@ -2328,7 +2325,7 @@
         <v>9.1666666666666674E-2</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J31" s="7">
         <v>109</v>
@@ -2338,18 +2335,18 @@
         <v>109</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>13</v>
@@ -2365,7 +2362,7 @@
         <v>0.19999999999999996</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J32" s="7">
         <v>100</v>
@@ -2375,21 +2372,21 @@
         <v>100</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E33" s="7">
         <v>115</v>
@@ -2402,7 +2399,7 @@
         <v>4.3478260869565188E-2</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J33" s="7">
         <v>110</v>
@@ -2412,18 +2409,18 @@
         <v>110</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>13</v>
@@ -2439,7 +2436,7 @@
         <v>0.18181818181818177</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J34" s="7">
         <v>90</v>
@@ -2449,18 +2446,18 @@
         <v>90</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>13</v>
@@ -2476,7 +2473,7 @@
         <v>0.19999999999999996</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J35" s="7">
         <v>96</v>
@@ -2486,21 +2483,21 @@
         <v>96</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E36" s="7">
         <v>110</v>
@@ -2513,7 +2510,7 @@
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J36" s="7">
         <v>99</v>
@@ -2523,18 +2520,18 @@
         <v>99</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>38</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>9</v>
@@ -2550,7 +2547,7 @@
         <v>9.5238095238095233E-2</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J37" s="7">
         <v>95</v>
@@ -2563,16 +2560,16 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>44</v>
+        <v>232</v>
       </c>
       <c r="E38" s="7">
         <v>120</v>
@@ -2585,7 +2582,7 @@
         <v>0.17500000000000004</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J38" s="7">
         <v>99</v>
@@ -2595,21 +2592,21 @@
         <v>99</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="E39" s="7">
         <v>115</v>
@@ -2622,7 +2619,7 @@
         <v>8.6956521739130488E-2</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J39" s="7">
         <v>105</v>
@@ -2632,18 +2629,18 @@
         <v>105</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>24</v>
@@ -2659,7 +2656,7 @@
         <v>0</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J40" s="7">
         <v>74</v>
@@ -2669,21 +2666,21 @@
         <v>74</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E41" s="7">
         <v>115</v>
@@ -2696,7 +2693,7 @@
         <v>0.19999999999999996</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J41" s="7">
         <v>92</v>
@@ -2706,18 +2703,18 @@
         <v>92</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>9</v>
@@ -2733,7 +2730,7 @@
         <v>0.15000000000000002</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J42" s="7">
         <v>85</v>
@@ -2743,21 +2740,21 @@
         <v>85</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E43" s="7">
         <v>135</v>
@@ -2770,7 +2767,7 @@
         <v>9.6296296296296324E-2</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J43" s="7">
         <v>122</v>
@@ -2780,21 +2777,21 @@
         <v>122</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E44" s="7">
         <v>110</v>
@@ -2807,7 +2804,7 @@
         <v>0.16363636363636369</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J44" s="7">
         <v>92</v>
@@ -2817,18 +2814,18 @@
         <v>92</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>13</v>
@@ -2844,7 +2841,7 @@
         <v>0.19999999999999996</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J45" s="7">
         <v>50</v>
@@ -2854,18 +2851,18 @@
         <v>50</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>16</v>
@@ -2881,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J46" s="7">
         <v>105</v>
@@ -2891,18 +2888,18 @@
         <v>105</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>24</v>
@@ -2918,7 +2915,7 @@
         <v>9.7560975609756073E-2</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J47" s="7">
         <v>74</v>
@@ -2928,21 +2925,21 @@
         <v>74</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>44</v>
+        <v>232</v>
       </c>
       <c r="E48" s="7">
         <v>99</v>
@@ -2955,7 +2952,7 @@
         <v>0.15151515151515149</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J48" s="7">
         <v>84</v>
@@ -2965,18 +2962,18 @@
         <v>84</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>16</v>
@@ -2992,7 +2989,7 @@
         <v>0.13043478260869568</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J49" s="7">
         <v>100</v>
@@ -3002,18 +2999,18 @@
         <v>100</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>13</v>
@@ -3029,7 +3026,7 @@
         <v>0.19999999999999996</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J50" s="7">
         <v>50</v>
@@ -3039,18 +3036,18 @@
         <v>50</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>9</v>
@@ -3066,7 +3063,7 @@
         <v>0.10101010101010099</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J51" s="7">
         <v>89</v>
@@ -3076,18 +3073,18 @@
         <v>89</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>41</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>9</v>
@@ -3103,7 +3100,7 @@
         <v>0.10101010101010099</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J52" s="7">
         <v>89</v>
@@ -3113,18 +3110,18 @@
         <v>89</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>41</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>43</v>
@@ -3140,7 +3137,7 @@
         <v>0.10769230769230764</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J53" s="7">
         <v>58</v>
@@ -3150,18 +3147,18 @@
         <v>58</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>41</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>24</v>
@@ -3177,7 +3174,7 @@
         <v>8.2352941176470629E-2</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J54" s="7">
         <v>78</v>
@@ -3187,18 +3184,18 @@
         <v>78</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>43</v>
@@ -3214,7 +3211,7 @@
         <v>0</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J55" s="7">
         <v>89</v>
@@ -3224,18 +3221,18 @@
         <v>89</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>43</v>
@@ -3251,7 +3248,7 @@
         <v>0.10344827586206895</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J56" s="7">
         <v>52</v>
@@ -3261,18 +3258,18 @@
         <v>52</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>41</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>9</v>
@@ -3288,7 +3285,7 @@
         <v>0.1775147928994083</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J57" s="7">
         <v>139</v>
@@ -3298,7 +3295,7 @@
         <v>139</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/catalogo_mikado.xlsx
+++ b/catalogo_mikado.xlsx
@@ -120,9 +120,6 @@
     <t>CELIMAX</t>
   </si>
   <si>
-    <t>DR ALTHEA</t>
-  </si>
-  <si>
     <t>MARY &amp; MAY</t>
   </si>
   <si>
@@ -721,6 +718,9 @@
   </si>
   <si>
     <t>Contorno de Ojos</t>
+  </si>
+  <si>
+    <t>DR. ALTHEA</t>
   </si>
 </sst>
 </file>
@@ -1218,13 +1218,13 @@
         <v>7</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="M1" s="9" t="s">
         <v>229</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>230</v>
       </c>
       <c r="N1" s="2">
         <f>SUM(F2:F937)</f>
@@ -1236,10 +1236,10 @@
         <v>8</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>9</v>
@@ -1265,7 +1265,7 @@
         <v>84</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -1276,7 +1276,7 @@
         <v>12</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>13</v>
@@ -1302,7 +1302,7 @@
         <v>88</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -1310,10 +1310,10 @@
         <v>15</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>16</v>
@@ -1339,7 +1339,7 @@
         <v>89</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M4" s="11"/>
     </row>
@@ -1348,10 +1348,10 @@
         <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>13</v>
@@ -1377,7 +1377,7 @@
         <v>92</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -1385,10 +1385,10 @@
         <v>20</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>21</v>
@@ -1414,7 +1414,7 @@
         <v>75</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -1422,10 +1422,10 @@
         <v>23</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>24</v>
@@ -1451,18 +1451,18 @@
         <v>99</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>27</v>
@@ -1488,18 +1488,18 @@
         <v>100</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>27</v>
@@ -1525,18 +1525,18 @@
         <v>100</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>13</v>
@@ -1552,7 +1552,7 @@
         <v>0.20799999999999996</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J10" s="7">
         <v>99</v>
@@ -1562,21 +1562,21 @@
         <v>99</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E11" s="7">
         <v>90</v>
@@ -1589,7 +1589,7 @@
         <v>6.6666666666666652E-2</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J11" s="7">
         <v>84</v>
@@ -1599,18 +1599,18 @@
         <v>84</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>13</v>
@@ -1626,7 +1626,7 @@
         <v>0.19999999999999996</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J12" s="7">
         <v>20</v>
@@ -1636,18 +1636,18 @@
         <v>20</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>9</v>
@@ -1663,7 +1663,7 @@
         <v>7.999999999999996E-2</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J13" s="7">
         <v>92</v>
@@ -1673,21 +1673,21 @@
         <v>92</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E14" s="7">
         <v>110</v>
@@ -1700,7 +1700,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J14" s="7">
         <v>110</v>
@@ -1713,13 +1713,13 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>24</v>
@@ -1735,7 +1735,7 @@
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J15" s="7">
         <v>99</v>
@@ -1745,18 +1745,18 @@
         <v>99</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>24</v>
@@ -1772,7 +1772,7 @@
         <v>5.7142857142857162E-2</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J16" s="7">
         <v>99</v>
@@ -1782,18 +1782,18 @@
         <v>99</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>13</v>
@@ -1809,7 +1809,7 @@
         <v>9.5238095238095233E-2</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J17" s="7">
         <v>95</v>
@@ -1819,18 +1819,18 @@
         <v>95</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>9</v>
@@ -1846,7 +1846,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J18" s="7">
         <v>92</v>
@@ -1856,21 +1856,21 @@
         <v>92</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E19" s="7">
         <v>125</v>
@@ -1883,7 +1883,7 @@
         <v>0.20799999999999996</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J19" s="7">
         <v>99</v>
@@ -1893,18 +1893,18 @@
         <v>99</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>13</v>
@@ -1920,7 +1920,7 @@
         <v>0.1428571428571429</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J20" s="7">
         <v>120</v>
@@ -1930,18 +1930,18 @@
         <v>120</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>13</v>
@@ -1957,7 +1957,7 @@
         <v>0.16363636363636369</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J21" s="7">
         <v>92</v>
@@ -1967,18 +1967,18 @@
         <v>92</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>13</v>
@@ -1994,7 +1994,7 @@
         <v>0.19230769230769229</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J22" s="7">
         <v>105</v>
@@ -2004,21 +2004,21 @@
         <v>105</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>32</v>
+        <v>232</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E23" s="7">
         <v>100</v>
@@ -2031,7 +2031,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J23" s="7">
         <v>100</v>
@@ -2041,18 +2041,18 @@
         <v>100</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>16</v>
@@ -2068,7 +2068,7 @@
         <v>8.4033613445378186E-2</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J24" s="7">
         <v>109</v>
@@ -2078,18 +2078,18 @@
         <v>109</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>21</v>
@@ -2105,7 +2105,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J25" s="7">
         <v>128</v>
@@ -2115,18 +2115,18 @@
         <v>128</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>21</v>
@@ -2142,7 +2142,7 @@
         <v>0.15384615384615385</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J26" s="7">
         <v>22</v>
@@ -2152,18 +2152,18 @@
         <v>22</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>21</v>
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J27" s="7">
         <v>109</v>
@@ -2189,21 +2189,21 @@
         <v>109</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E28" s="7">
         <v>109</v>
@@ -2216,7 +2216,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J28" s="7">
         <v>109</v>
@@ -2226,21 +2226,21 @@
         <v>109</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E29" s="7">
         <v>25</v>
@@ -2253,7 +2253,7 @@
         <v>0.19999999999999996</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J29" s="7">
         <v>20</v>
@@ -2266,13 +2266,13 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>24</v>
@@ -2288,7 +2288,7 @@
         <v>0</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J30" s="7">
         <v>102</v>
@@ -2298,21 +2298,21 @@
         <v>102</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E31" s="7">
         <v>120</v>
@@ -2325,7 +2325,7 @@
         <v>9.1666666666666674E-2</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J31" s="7">
         <v>109</v>
@@ -2335,18 +2335,18 @@
         <v>109</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>13</v>
@@ -2362,7 +2362,7 @@
         <v>0.19999999999999996</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J32" s="7">
         <v>100</v>
@@ -2372,21 +2372,21 @@
         <v>100</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E33" s="7">
         <v>115</v>
@@ -2399,7 +2399,7 @@
         <v>4.3478260869565188E-2</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J33" s="7">
         <v>110</v>
@@ -2409,18 +2409,18 @@
         <v>110</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>13</v>
@@ -2436,7 +2436,7 @@
         <v>0.18181818181818177</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J34" s="7">
         <v>90</v>
@@ -2446,18 +2446,18 @@
         <v>90</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>13</v>
@@ -2473,7 +2473,7 @@
         <v>0.19999999999999996</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J35" s="7">
         <v>96</v>
@@ -2483,21 +2483,21 @@
         <v>96</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E36" s="7">
         <v>110</v>
@@ -2510,7 +2510,7 @@
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J36" s="7">
         <v>99</v>
@@ -2520,18 +2520,18 @@
         <v>99</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>9</v>
@@ -2547,7 +2547,7 @@
         <v>9.5238095238095233E-2</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J37" s="7">
         <v>95</v>
@@ -2560,16 +2560,16 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E38" s="7">
         <v>120</v>
@@ -2582,7 +2582,7 @@
         <v>0.17500000000000004</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J38" s="7">
         <v>99</v>
@@ -2592,18 +2592,18 @@
         <v>99</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>13</v>
@@ -2619,7 +2619,7 @@
         <v>8.6956521739130488E-2</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J39" s="7">
         <v>105</v>
@@ -2629,18 +2629,18 @@
         <v>105</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>24</v>
@@ -2656,7 +2656,7 @@
         <v>0</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J40" s="7">
         <v>74</v>
@@ -2666,21 +2666,21 @@
         <v>74</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E41" s="7">
         <v>115</v>
@@ -2693,7 +2693,7 @@
         <v>0.19999999999999996</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J41" s="7">
         <v>92</v>
@@ -2703,18 +2703,18 @@
         <v>92</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>9</v>
@@ -2730,7 +2730,7 @@
         <v>0.15000000000000002</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J42" s="7">
         <v>85</v>
@@ -2740,21 +2740,21 @@
         <v>85</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E43" s="7">
         <v>135</v>
@@ -2767,7 +2767,7 @@
         <v>9.6296296296296324E-2</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J43" s="7">
         <v>122</v>
@@ -2777,21 +2777,21 @@
         <v>122</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E44" s="7">
         <v>110</v>
@@ -2804,7 +2804,7 @@
         <v>0.16363636363636369</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J44" s="7">
         <v>92</v>
@@ -2814,18 +2814,18 @@
         <v>92</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>13</v>
@@ -2841,7 +2841,7 @@
         <v>0.19999999999999996</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J45" s="7">
         <v>50</v>
@@ -2851,18 +2851,18 @@
         <v>50</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>16</v>
@@ -2878,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J46" s="7">
         <v>105</v>
@@ -2888,18 +2888,18 @@
         <v>105</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>24</v>
@@ -2915,7 +2915,7 @@
         <v>9.7560975609756073E-2</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J47" s="7">
         <v>74</v>
@@ -2925,21 +2925,21 @@
         <v>74</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E48" s="7">
         <v>99</v>
@@ -2952,7 +2952,7 @@
         <v>0.15151515151515149</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J48" s="7">
         <v>84</v>
@@ -2962,18 +2962,18 @@
         <v>84</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>16</v>
@@ -2989,7 +2989,7 @@
         <v>0.13043478260869568</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J49" s="7">
         <v>100</v>
@@ -2999,18 +2999,18 @@
         <v>100</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>13</v>
@@ -3026,7 +3026,7 @@
         <v>0.19999999999999996</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J50" s="7">
         <v>50</v>
@@ -3036,18 +3036,18 @@
         <v>50</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>9</v>
@@ -3063,7 +3063,7 @@
         <v>0.10101010101010099</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J51" s="7">
         <v>89</v>
@@ -3073,18 +3073,18 @@
         <v>89</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>9</v>
@@ -3100,7 +3100,7 @@
         <v>0.10101010101010099</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J52" s="7">
         <v>89</v>
@@ -3110,21 +3110,21 @@
         <v>89</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E53" s="7">
         <v>65</v>
@@ -3137,7 +3137,7 @@
         <v>0.10769230769230764</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J53" s="7">
         <v>58</v>
@@ -3147,18 +3147,18 @@
         <v>58</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>24</v>
@@ -3174,7 +3174,7 @@
         <v>8.2352941176470629E-2</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J54" s="7">
         <v>78</v>
@@ -3184,21 +3184,21 @@
         <v>78</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B55" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D55" s="6" t="s">
         <v>42</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>43</v>
       </c>
       <c r="E55" s="7">
         <v>89</v>
@@ -3211,7 +3211,7 @@
         <v>0</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J55" s="7">
         <v>89</v>
@@ -3221,21 +3221,21 @@
         <v>89</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B56" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D56" s="6" t="s">
         <v>42</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>43</v>
       </c>
       <c r="E56" s="7">
         <v>58</v>
@@ -3248,7 +3248,7 @@
         <v>0.10344827586206895</v>
       </c>
       <c r="H56" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J56" s="7">
         <v>52</v>
@@ -3258,18 +3258,18 @@
         <v>52</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>9</v>
@@ -3285,7 +3285,7 @@
         <v>0.1775147928994083</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J57" s="7">
         <v>139</v>
@@ -3295,7 +3295,7 @@
         <v>139</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
